--- a/Predictions/timestamps_typical_cnn.xlsx
+++ b/Predictions/timestamps_typical_cnn.xlsx
@@ -462,4082 +462,4082 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38.34373092651367</v>
+        <v>43.87253189086914</v>
       </c>
       <c r="B2" t="n">
-        <v>41.13775634765625</v>
+        <v>39.31160736083984</v>
       </c>
       <c r="C2" t="n">
-        <v>2.925385236740112</v>
+        <v>15.1259069442749</v>
       </c>
       <c r="D2" t="n">
-        <v>6.661154747009277</v>
+        <v>11.91978454589844</v>
       </c>
       <c r="E2" t="n">
-        <v>-12.751877784729</v>
+        <v>-17.46536445617676</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.14040851593018</v>
+        <v>-21.33661842346191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38.05833053588867</v>
+        <v>43.56560897827148</v>
       </c>
       <c r="B3" t="n">
-        <v>41.94973754882812</v>
+        <v>40.15723419189453</v>
       </c>
       <c r="C3" t="n">
-        <v>5.053248405456543</v>
+        <v>18.09334373474121</v>
       </c>
       <c r="D3" t="n">
-        <v>9.320132255554199</v>
+        <v>15.11086750030518</v>
       </c>
       <c r="E3" t="n">
-        <v>-14.85113620758057</v>
+        <v>-19.46195793151855</v>
       </c>
       <c r="F3" t="n">
-        <v>-13.65739917755127</v>
+        <v>-22.75368690490723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37.13600921630859</v>
+        <v>42.91502380371094</v>
       </c>
       <c r="B4" t="n">
-        <v>42.05736923217773</v>
+        <v>39.66020584106445</v>
       </c>
       <c r="C4" t="n">
-        <v>7.032229423522949</v>
+        <v>21.80851936340332</v>
       </c>
       <c r="D4" t="n">
-        <v>12.20729446411133</v>
+        <v>17.12820243835449</v>
       </c>
       <c r="E4" t="n">
-        <v>-16.01135444641113</v>
+        <v>-19.10151100158691</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.18101501464844</v>
+        <v>-23.71088790893555</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36.02739715576172</v>
+        <v>41.64968872070312</v>
       </c>
       <c r="B5" t="n">
-        <v>41.20976638793945</v>
+        <v>38.12044906616211</v>
       </c>
       <c r="C5" t="n">
-        <v>8.488329887390137</v>
+        <v>23.51621055603027</v>
       </c>
       <c r="D5" t="n">
-        <v>14.76255702972412</v>
+        <v>19.57667350769043</v>
       </c>
       <c r="E5" t="n">
-        <v>-15.53852462768555</v>
+        <v>-16.87899017333984</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.06051635742188</v>
+        <v>-24.01483917236328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>34.73540115356445</v>
+        <v>39.42227935791016</v>
       </c>
       <c r="B6" t="n">
-        <v>40.283447265625</v>
+        <v>35.71238327026367</v>
       </c>
       <c r="C6" t="n">
-        <v>9.758258819580078</v>
+        <v>24.8575267791748</v>
       </c>
       <c r="D6" t="n">
-        <v>17.61728096008301</v>
+        <v>20.33008766174316</v>
       </c>
       <c r="E6" t="n">
-        <v>-15.68052768707275</v>
+        <v>-14.62795543670654</v>
       </c>
       <c r="F6" t="n">
-        <v>-14.25555896759033</v>
+        <v>-21.74004936218262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32.95729064941406</v>
+        <v>37.80946731567383</v>
       </c>
       <c r="B7" t="n">
-        <v>39.59439468383789</v>
+        <v>34.91099548339844</v>
       </c>
       <c r="C7" t="n">
-        <v>10.6554651260376</v>
+        <v>24.76050186157227</v>
       </c>
       <c r="D7" t="n">
-        <v>19.52559280395508</v>
+        <v>20.37893104553223</v>
       </c>
       <c r="E7" t="n">
-        <v>-11.86659622192383</v>
+        <v>-10.73952198028564</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.52970695495605</v>
+        <v>-18.21557807922363</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31.28656005859375</v>
+        <v>35.52494049072266</v>
       </c>
       <c r="B8" t="n">
-        <v>37.92689895629883</v>
+        <v>32.06747817993164</v>
       </c>
       <c r="C8" t="n">
-        <v>11.59963226318359</v>
+        <v>23.77803039550781</v>
       </c>
       <c r="D8" t="n">
-        <v>20.46550941467285</v>
+        <v>20.23916435241699</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.199234008789062</v>
+        <v>-6.864798545837402</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.522261142730713</v>
+        <v>-14.07390213012695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>29.39972686767578</v>
+        <v>32.48527526855469</v>
       </c>
       <c r="B9" t="n">
-        <v>35.56827926635742</v>
+        <v>28.99556159973145</v>
       </c>
       <c r="C9" t="n">
-        <v>11.7785472869873</v>
+        <v>22.91994857788086</v>
       </c>
       <c r="D9" t="n">
-        <v>21.0797061920166</v>
+        <v>18.34366416931152</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.071544170379639</v>
+        <v>-3.114745140075684</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.36723780632019</v>
+        <v>-12.33849430084229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27.77545738220215</v>
+        <v>30.1829948425293</v>
       </c>
       <c r="B10" t="n">
-        <v>33.9565544128418</v>
+        <v>25.03452301025391</v>
       </c>
       <c r="C10" t="n">
-        <v>11.35235691070557</v>
+        <v>20.61233139038086</v>
       </c>
       <c r="D10" t="n">
-        <v>20.92632675170898</v>
+        <v>15.78058242797852</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.374815940856934</v>
+        <v>-0.9883084297180176</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9724616408348083</v>
+        <v>-8.661165237426758</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24.97278594970703</v>
+        <v>26.6367130279541</v>
       </c>
       <c r="B11" t="n">
-        <v>31.35473823547363</v>
+        <v>22.00670051574707</v>
       </c>
       <c r="C11" t="n">
-        <v>10.79228782653809</v>
+        <v>17.8688907623291</v>
       </c>
       <c r="D11" t="n">
-        <v>19.90657615661621</v>
+        <v>13.81616878509521</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3442411422729492</v>
+        <v>1.300605773925781</v>
       </c>
       <c r="F11" t="n">
-        <v>3.577927589416504</v>
+        <v>-7.052166938781738</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23.0560245513916</v>
+        <v>23.34903907775879</v>
       </c>
       <c r="B12" t="n">
-        <v>28.75998497009277</v>
+        <v>19.13638687133789</v>
       </c>
       <c r="C12" t="n">
-        <v>10.02844905853271</v>
+        <v>15.36779403686523</v>
       </c>
       <c r="D12" t="n">
-        <v>18.85569000244141</v>
+        <v>10.86716842651367</v>
       </c>
       <c r="E12" t="n">
-        <v>1.599597930908203</v>
+        <v>1.90013313293457</v>
       </c>
       <c r="F12" t="n">
-        <v>5.230973243713379</v>
+        <v>-5.638071537017822</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20.77594757080078</v>
+        <v>20.50604057312012</v>
       </c>
       <c r="B13" t="n">
-        <v>26.45898056030273</v>
+        <v>15.69158267974854</v>
       </c>
       <c r="C13" t="n">
-        <v>9.003239631652832</v>
+        <v>12.2009973526001</v>
       </c>
       <c r="D13" t="n">
-        <v>17.46026992797852</v>
+        <v>9.470370292663574</v>
       </c>
       <c r="E13" t="n">
-        <v>3.177431106567383</v>
+        <v>3.23652458190918</v>
       </c>
       <c r="F13" t="n">
-        <v>7.498630523681641</v>
+        <v>-4.571367740631104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18.65548324584961</v>
+        <v>17.81026649475098</v>
       </c>
       <c r="B14" t="n">
-        <v>24.02921485900879</v>
+        <v>13.2100772857666</v>
       </c>
       <c r="C14" t="n">
-        <v>8.029328346252441</v>
+        <v>10.3966588973999</v>
       </c>
       <c r="D14" t="n">
-        <v>16.84336280822754</v>
+        <v>6.596880912780762</v>
       </c>
       <c r="E14" t="n">
-        <v>5.049484252929688</v>
+        <v>4.810447692871094</v>
       </c>
       <c r="F14" t="n">
-        <v>9.10530948638916</v>
+        <v>-2.820802927017212</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16.51733207702637</v>
+        <v>14.18607616424561</v>
       </c>
       <c r="B15" t="n">
-        <v>21.64999008178711</v>
+        <v>9.768886566162109</v>
       </c>
       <c r="C15" t="n">
-        <v>7.126618385314941</v>
+        <v>9.100543022155762</v>
       </c>
       <c r="D15" t="n">
-        <v>15.47488498687744</v>
+        <v>5.503996849060059</v>
       </c>
       <c r="E15" t="n">
-        <v>6.767851829528809</v>
+        <v>5.393227577209473</v>
       </c>
       <c r="F15" t="n">
-        <v>10.72664833068848</v>
+        <v>-1.24529755115509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14.80623817443848</v>
+        <v>11.3820219039917</v>
       </c>
       <c r="B16" t="n">
-        <v>19.39018630981445</v>
+        <v>6.603270530700684</v>
       </c>
       <c r="C16" t="n">
-        <v>6.529288291931152</v>
+        <v>6.163233757019043</v>
       </c>
       <c r="D16" t="n">
-        <v>14.52809715270996</v>
+        <v>4.152646064758301</v>
       </c>
       <c r="E16" t="n">
-        <v>8.736023902893066</v>
+        <v>6.91171932220459</v>
       </c>
       <c r="F16" t="n">
-        <v>12.54460525512695</v>
+        <v>2.981017112731934</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12.63525295257568</v>
+        <v>8.728228569030762</v>
       </c>
       <c r="B17" t="n">
-        <v>17.16504859924316</v>
+        <v>4.236149787902832</v>
       </c>
       <c r="C17" t="n">
-        <v>5.529370307922363</v>
+        <v>5.730433464050293</v>
       </c>
       <c r="D17" t="n">
-        <v>13.00558376312256</v>
+        <v>3.828950166702271</v>
       </c>
       <c r="E17" t="n">
-        <v>10.16302967071533</v>
+        <v>9.329163551330566</v>
       </c>
       <c r="F17" t="n">
-        <v>13.94268226623535</v>
+        <v>5.295392990112305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11.13693904876709</v>
+        <v>5.819559574127197</v>
       </c>
       <c r="B18" t="n">
-        <v>15.16847610473633</v>
+        <v>1.938269376754761</v>
       </c>
       <c r="C18" t="n">
-        <v>4.964140892028809</v>
+        <v>4.953320503234863</v>
       </c>
       <c r="D18" t="n">
-        <v>12.7505464553833</v>
+        <v>4.22489070892334</v>
       </c>
       <c r="E18" t="n">
-        <v>12.27386379241943</v>
+        <v>11.81319713592529</v>
       </c>
       <c r="F18" t="n">
-        <v>15.98422813415527</v>
+        <v>7.487289428710938</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9.377405166625977</v>
+        <v>3.94523286819458</v>
       </c>
       <c r="B19" t="n">
-        <v>13.54182052612305</v>
+        <v>-0.5760967135429382</v>
       </c>
       <c r="C19" t="n">
-        <v>4.555336952209473</v>
+        <v>4.675402641296387</v>
       </c>
       <c r="D19" t="n">
-        <v>11.98431968688965</v>
+        <v>2.97692608833313</v>
       </c>
       <c r="E19" t="n">
-        <v>14.01651668548584</v>
+        <v>13.9365701675415</v>
       </c>
       <c r="F19" t="n">
-        <v>18.33621025085449</v>
+        <v>10.42029762268066</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7.957277774810791</v>
+        <v>0.705170214176178</v>
       </c>
       <c r="B20" t="n">
-        <v>12.15233993530273</v>
+        <v>-4.311886787414551</v>
       </c>
       <c r="C20" t="n">
-        <v>4.899184226989746</v>
+        <v>5.02883243560791</v>
       </c>
       <c r="D20" t="n">
-        <v>12.26275062561035</v>
+        <v>3.187613725662231</v>
       </c>
       <c r="E20" t="n">
-        <v>15.23341274261475</v>
+        <v>16.88067436218262</v>
       </c>
       <c r="F20" t="n">
-        <v>21.00344276428223</v>
+        <v>13.10464859008789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6.45165491104126</v>
+        <v>0.1613984704017639</v>
       </c>
       <c r="B21" t="n">
-        <v>11.19570541381836</v>
+        <v>-5.822001457214355</v>
       </c>
       <c r="C21" t="n">
-        <v>5.635924339294434</v>
+        <v>5.748087882995605</v>
       </c>
       <c r="D21" t="n">
-        <v>12.6297435760498</v>
+        <v>3.95215916633606</v>
       </c>
       <c r="E21" t="n">
-        <v>16.84989547729492</v>
+        <v>20.69091987609863</v>
       </c>
       <c r="F21" t="n">
-        <v>24.00651741027832</v>
+        <v>15.58873176574707</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4.786671161651611</v>
+        <v>-1.341592311859131</v>
       </c>
       <c r="B22" t="n">
-        <v>10.34582138061523</v>
+        <v>-7.935389518737793</v>
       </c>
       <c r="C22" t="n">
-        <v>6.827815055847168</v>
+        <v>6.678704261779785</v>
       </c>
       <c r="D22" t="n">
-        <v>13.39369297027588</v>
+        <v>4.646182060241699</v>
       </c>
       <c r="E22" t="n">
-        <v>17.08839416503906</v>
+        <v>21.21604347229004</v>
       </c>
       <c r="F22" t="n">
-        <v>26.12407875061035</v>
+        <v>17.42180824279785</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3.655685901641846</v>
+        <v>-2.656117916107178</v>
       </c>
       <c r="B23" t="n">
-        <v>9.246870040893555</v>
+        <v>-10.37640285491943</v>
       </c>
       <c r="C23" t="n">
-        <v>7.998265266418457</v>
+        <v>7.929909706115723</v>
       </c>
       <c r="D23" t="n">
-        <v>15.04872894287109</v>
+        <v>6.677380561828613</v>
       </c>
       <c r="E23" t="n">
-        <v>17.33306503295898</v>
+        <v>21.59668922424316</v>
       </c>
       <c r="F23" t="n">
-        <v>28.36324119567871</v>
+        <v>17.81032562255859</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.030596256256104</v>
+        <v>-3.843017101287842</v>
       </c>
       <c r="B24" t="n">
-        <v>7.953313827514648</v>
+        <v>-11.96115016937256</v>
       </c>
       <c r="C24" t="n">
-        <v>9.123722076416016</v>
+        <v>11.64692783355713</v>
       </c>
       <c r="D24" t="n">
-        <v>15.85858917236328</v>
+        <v>7.71048641204834</v>
       </c>
       <c r="E24" t="n">
-        <v>16.96927452087402</v>
+        <v>21.89765930175781</v>
       </c>
       <c r="F24" t="n">
-        <v>29.85317039489746</v>
+        <v>16.43814468383789</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.397924900054932</v>
+        <v>-4.051126003265381</v>
       </c>
       <c r="B25" t="n">
-        <v>6.903658866882324</v>
+        <v>-12.30798244476318</v>
       </c>
       <c r="C25" t="n">
-        <v>11.09852600097656</v>
+        <v>14.6584005355835</v>
       </c>
       <c r="D25" t="n">
-        <v>17.44896125793457</v>
+        <v>10.3696813583374</v>
       </c>
       <c r="E25" t="n">
-        <v>15.19190120697021</v>
+        <v>17.12217330932617</v>
       </c>
       <c r="F25" t="n">
-        <v>31.18976020812988</v>
+        <v>13.22016906738281</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.8828588128089905</v>
+        <v>-3.185235500335693</v>
       </c>
       <c r="B26" t="n">
-        <v>5.127640724182129</v>
+        <v>-11.87984371185303</v>
       </c>
       <c r="C26" t="n">
-        <v>13.67200088500977</v>
+        <v>18.90987968444824</v>
       </c>
       <c r="D26" t="n">
-        <v>19.27194404602051</v>
+        <v>13.61728572845459</v>
       </c>
       <c r="E26" t="n">
-        <v>10.24754619598389</v>
+        <v>10.09364032745361</v>
       </c>
       <c r="F26" t="n">
-        <v>29.51595115661621</v>
+        <v>7.450211524963379</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.3496251702308655</v>
+        <v>-2.258468151092529</v>
       </c>
       <c r="B27" t="n">
-        <v>4.477755546569824</v>
+        <v>-12.62634563446045</v>
       </c>
       <c r="C27" t="n">
-        <v>16.62936973571777</v>
+        <v>24.49924278259277</v>
       </c>
       <c r="D27" t="n">
-        <v>21.91444206237793</v>
+        <v>17.46397399902344</v>
       </c>
       <c r="E27" t="n">
-        <v>2.950709342956543</v>
+        <v>0.7097616195678711</v>
       </c>
       <c r="F27" t="n">
-        <v>25.03232574462891</v>
+        <v>0.1314048171043396</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.09156280755996704</v>
+        <v>-0.9988684058189392</v>
       </c>
       <c r="B28" t="n">
-        <v>4.278744697570801</v>
+        <v>-11.28583812713623</v>
       </c>
       <c r="C28" t="n">
-        <v>20.44844436645508</v>
+        <v>29.97283554077148</v>
       </c>
       <c r="D28" t="n">
-        <v>25.65978050231934</v>
+        <v>23.32414054870605</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.235471248626709</v>
+        <v>-11.54798698425293</v>
       </c>
       <c r="F28" t="n">
-        <v>18.40815544128418</v>
+        <v>-8.134461402893066</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.985849857330322</v>
+        <v>0.6974931359291077</v>
       </c>
       <c r="B29" t="n">
-        <v>4.032513618469238</v>
+        <v>-9.588507652282715</v>
       </c>
       <c r="C29" t="n">
-        <v>25.8893985748291</v>
+        <v>36.4217529296875</v>
       </c>
       <c r="D29" t="n">
-        <v>29.77412986755371</v>
+        <v>27.96015357971191</v>
       </c>
       <c r="E29" t="n">
-        <v>-19.51303100585938</v>
+        <v>-22.66125679016113</v>
       </c>
       <c r="F29" t="n">
-        <v>6.872127532958984</v>
+        <v>-17.21187591552734</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3.564249515533447</v>
+        <v>2.397797107696533</v>
       </c>
       <c r="B30" t="n">
-        <v>5.552428245544434</v>
+        <v>-6.620774269104004</v>
       </c>
       <c r="C30" t="n">
-        <v>32.10245132446289</v>
+        <v>43.08254623413086</v>
       </c>
       <c r="D30" t="n">
-        <v>35.85738754272461</v>
+        <v>34.12766647338867</v>
       </c>
       <c r="E30" t="n">
-        <v>-31.45121002197266</v>
+        <v>-32.41366577148438</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.248575687408447</v>
+        <v>-24.74967575073242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5.637892246246338</v>
+        <v>6.30178689956665</v>
       </c>
       <c r="B31" t="n">
-        <v>8.203118324279785</v>
+        <v>-3.845330476760864</v>
       </c>
       <c r="C31" t="n">
-        <v>37.81624221801758</v>
+        <v>48.41532516479492</v>
       </c>
       <c r="D31" t="n">
-        <v>42.98246765136719</v>
+        <v>40.23344421386719</v>
       </c>
       <c r="E31" t="n">
-        <v>-40.31135940551758</v>
+        <v>-38.88641357421875</v>
       </c>
       <c r="F31" t="n">
-        <v>-17.77892112731934</v>
+        <v>-31.08890533447266</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9.200091361999512</v>
+        <v>10.65081310272217</v>
       </c>
       <c r="B32" t="n">
-        <v>10.94562721252441</v>
+        <v>-0.04138297215104103</v>
       </c>
       <c r="C32" t="n">
-        <v>44.3884162902832</v>
+        <v>54.75432968139648</v>
       </c>
       <c r="D32" t="n">
-        <v>49.2047233581543</v>
+        <v>47.38703155517578</v>
       </c>
       <c r="E32" t="n">
-        <v>-43.32699203491211</v>
+        <v>-41.45791625976562</v>
       </c>
       <c r="F32" t="n">
-        <v>-26.44643211364746</v>
+        <v>-32.46384048461914</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13.25861740112305</v>
+        <v>14.22915935516357</v>
       </c>
       <c r="B33" t="n">
-        <v>14.07018375396729</v>
+        <v>4.492794990539551</v>
       </c>
       <c r="C33" t="n">
-        <v>49.29926300048828</v>
+        <v>60.63752365112305</v>
       </c>
       <c r="D33" t="n">
-        <v>54.8390007019043</v>
+        <v>52.56180572509766</v>
       </c>
       <c r="E33" t="n">
-        <v>-41.09056091308594</v>
+        <v>-40.72676086425781</v>
       </c>
       <c r="F33" t="n">
-        <v>-30.64229583740234</v>
+        <v>-31.96177101135254</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.75588035583496</v>
+        <v>18.01041793823242</v>
       </c>
       <c r="B34" t="n">
-        <v>17.97576141357422</v>
+        <v>8.62612247467041</v>
       </c>
       <c r="C34" t="n">
-        <v>52.66789245605469</v>
+        <v>65.39335632324219</v>
       </c>
       <c r="D34" t="n">
-        <v>60.20452499389648</v>
+        <v>57.33223724365234</v>
       </c>
       <c r="E34" t="n">
-        <v>-33.77572250366211</v>
+        <v>-34.95955276489258</v>
       </c>
       <c r="F34" t="n">
-        <v>-29.64621353149414</v>
+        <v>-29.28086090087891</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>19.98725128173828</v>
+        <v>23.21050453186035</v>
       </c>
       <c r="B35" t="n">
-        <v>21.57985305786133</v>
+        <v>12.67350578308105</v>
       </c>
       <c r="C35" t="n">
-        <v>53.87854385375977</v>
+        <v>68.53499603271484</v>
       </c>
       <c r="D35" t="n">
-        <v>62.07033538818359</v>
+        <v>58.66855239868164</v>
       </c>
       <c r="E35" t="n">
-        <v>-24.0627555847168</v>
+        <v>-27.61221885681152</v>
       </c>
       <c r="F35" t="n">
-        <v>-24.65387725830078</v>
+        <v>-24.65776634216309</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>23.25388717651367</v>
+        <v>26.21519088745117</v>
       </c>
       <c r="B36" t="n">
-        <v>24.82017707824707</v>
+        <v>16.95799255371094</v>
       </c>
       <c r="C36" t="n">
-        <v>53.90212631225586</v>
+        <v>67.76476287841797</v>
       </c>
       <c r="D36" t="n">
-        <v>63.26442718505859</v>
+        <v>61.39897918701172</v>
       </c>
       <c r="E36" t="n">
-        <v>-14.24916172027588</v>
+        <v>-19.30628967285156</v>
       </c>
       <c r="F36" t="n">
-        <v>-16.893798828125</v>
+        <v>-18.45437240600586</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>25.97440528869629</v>
+        <v>29.89160919189453</v>
       </c>
       <c r="B37" t="n">
-        <v>28.27960968017578</v>
+        <v>21.14091300964355</v>
       </c>
       <c r="C37" t="n">
-        <v>50.43149185180664</v>
+        <v>66.93428039550781</v>
       </c>
       <c r="D37" t="n">
-        <v>60.97900390625</v>
+        <v>60.6024284362793</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.045873165130615</v>
+        <v>-11.87093544006348</v>
       </c>
       <c r="F37" t="n">
-        <v>-9.464885711669922</v>
+        <v>-11.24550724029541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>28.05731201171875</v>
+        <v>32.50563430786133</v>
       </c>
       <c r="B38" t="n">
-        <v>31.0963191986084</v>
+        <v>24.06355476379395</v>
       </c>
       <c r="C38" t="n">
-        <v>46.73260116577148</v>
+        <v>63.85319900512695</v>
       </c>
       <c r="D38" t="n">
-        <v>58.56692123413086</v>
+        <v>57.83661651611328</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.687858104705811</v>
+        <v>-6.313706398010254</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.156953096389771</v>
+        <v>-7.863214015960693</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>30.36055374145508</v>
+        <v>34.57255172729492</v>
       </c>
       <c r="B39" t="n">
-        <v>33.00352096557617</v>
+        <v>26.80367469787598</v>
       </c>
       <c r="C39" t="n">
-        <v>40.2403678894043</v>
+        <v>58.08461761474609</v>
       </c>
       <c r="D39" t="n">
-        <v>53.87477111816406</v>
+        <v>54.16205978393555</v>
       </c>
       <c r="E39" t="n">
-        <v>1.653389930725098</v>
+        <v>-3.523447751998901</v>
       </c>
       <c r="F39" t="n">
-        <v>3.057342529296875</v>
+        <v>-4.959547519683838</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>31.73471069335938</v>
+        <v>35.35516738891602</v>
       </c>
       <c r="B40" t="n">
-        <v>35.93052291870117</v>
+        <v>28.37302017211914</v>
       </c>
       <c r="C40" t="n">
-        <v>34.05858612060547</v>
+        <v>51.64469909667969</v>
       </c>
       <c r="D40" t="n">
-        <v>48.50672912597656</v>
+        <v>47.24673461914062</v>
       </c>
       <c r="E40" t="n">
-        <v>2.919459342956543</v>
+        <v>-2.517172336578369</v>
       </c>
       <c r="F40" t="n">
-        <v>6.600927352905273</v>
+        <v>-3.025004863739014</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>32.85738754272461</v>
+        <v>36.65693664550781</v>
       </c>
       <c r="B41" t="n">
-        <v>37.58857727050781</v>
+        <v>29.86124610900879</v>
       </c>
       <c r="C41" t="n">
-        <v>27.63829040527344</v>
+        <v>43.1213264465332</v>
       </c>
       <c r="D41" t="n">
-        <v>42.24664688110352</v>
+        <v>40.43458557128906</v>
       </c>
       <c r="E41" t="n">
-        <v>3.112801551818848</v>
+        <v>-3.382030010223389</v>
       </c>
       <c r="F41" t="n">
-        <v>7.901412010192871</v>
+        <v>-3.303555250167847</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>33.84677505493164</v>
+        <v>36.27177047729492</v>
       </c>
       <c r="B42" t="n">
-        <v>38.65502166748047</v>
+        <v>31.17607307434082</v>
       </c>
       <c r="C42" t="n">
-        <v>20.4395923614502</v>
+        <v>35.08597946166992</v>
       </c>
       <c r="D42" t="n">
-        <v>34.40257263183594</v>
+        <v>31.47867012023926</v>
       </c>
       <c r="E42" t="n">
-        <v>2.219385147094727</v>
+        <v>-4.118978977203369</v>
       </c>
       <c r="F42" t="n">
-        <v>7.668350219726562</v>
+        <v>-4.676380157470703</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>34.16299819946289</v>
+        <v>37.56466293334961</v>
       </c>
       <c r="B43" t="n">
-        <v>39.2626953125</v>
+        <v>31.10212516784668</v>
       </c>
       <c r="C43" t="n">
-        <v>13.01781177520752</v>
+        <v>27.29387092590332</v>
       </c>
       <c r="D43" t="n">
-        <v>26.99516105651855</v>
+        <v>24.2707691192627</v>
       </c>
       <c r="E43" t="n">
-        <v>1.24190616607666</v>
+        <v>-7.149966239929199</v>
       </c>
       <c r="F43" t="n">
-        <v>5.984354019165039</v>
+        <v>-7.102152824401855</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>35.32689666748047</v>
+        <v>37.07899856567383</v>
       </c>
       <c r="B44" t="n">
-        <v>39.9071159362793</v>
+        <v>31.70507431030273</v>
       </c>
       <c r="C44" t="n">
-        <v>5.938097953796387</v>
+        <v>19.31755256652832</v>
       </c>
       <c r="D44" t="n">
-        <v>19.64663887023926</v>
+        <v>16.59301376342773</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1827788352966309</v>
+        <v>-9.192358016967773</v>
       </c>
       <c r="F44" t="n">
-        <v>3.911386489868164</v>
+        <v>-9.357359886169434</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>35.21659088134766</v>
+        <v>36.52230453491211</v>
       </c>
       <c r="B45" t="n">
-        <v>39.95203399658203</v>
+        <v>31.44748115539551</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4596965909004211</v>
+        <v>12.90974426269531</v>
       </c>
       <c r="D45" t="n">
-        <v>12.10364627838135</v>
+        <v>9.620408058166504</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5662221908569336</v>
+        <v>-10.21691513061523</v>
       </c>
       <c r="F45" t="n">
-        <v>2.686846733093262</v>
+        <v>-10.67685985565186</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>35.87989044189453</v>
+        <v>36.61140441894531</v>
       </c>
       <c r="B46" t="n">
-        <v>39.83810806274414</v>
+        <v>31.83555030822754</v>
       </c>
       <c r="C46" t="n">
-        <v>-3.974869966506958</v>
+        <v>8.732617378234863</v>
       </c>
       <c r="D46" t="n">
-        <v>5.352177619934082</v>
+        <v>5.286105155944824</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.9301390647888184</v>
+        <v>-12.11251926422119</v>
       </c>
       <c r="F46" t="n">
-        <v>1.53017795085907</v>
+        <v>-13.27818393707275</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>36.39965057373047</v>
+        <v>36.33021545410156</v>
       </c>
       <c r="B47" t="n">
-        <v>39.70807647705078</v>
+        <v>31.76885795593262</v>
       </c>
       <c r="C47" t="n">
-        <v>-6.24411678314209</v>
+        <v>6.309445381164551</v>
       </c>
       <c r="D47" t="n">
-        <v>1.664198994636536</v>
+        <v>1.426190495491028</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.389007091522217</v>
+        <v>-13.0783576965332</v>
       </c>
       <c r="F47" t="n">
-        <v>1.300700068473816</v>
+        <v>-13.95179653167725</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>36.91326141357422</v>
+        <v>37.20140838623047</v>
       </c>
       <c r="B48" t="n">
-        <v>39.44724273681641</v>
+        <v>31.75262260437012</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.356112480163574</v>
+        <v>5.150933265686035</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4872406721115112</v>
+        <v>0.8110877275466919</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.519798278808594</v>
+        <v>-13.31075859069824</v>
       </c>
       <c r="F48" t="n">
-        <v>1.212458491325378</v>
+        <v>-15.45533466339111</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>37.50703811645508</v>
+        <v>39.1028938293457</v>
       </c>
       <c r="B49" t="n">
-        <v>39.27846908569336</v>
+        <v>32.8728141784668</v>
       </c>
       <c r="C49" t="n">
-        <v>-6.295418739318848</v>
+        <v>4.842162132263184</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6918820142745972</v>
+        <v>0.4021483659744263</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.188679218292236</v>
+        <v>-13.59721946716309</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.05792862921953201</v>
+        <v>-16.36232948303223</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>38.16765213012695</v>
+        <v>41.54227447509766</v>
       </c>
       <c r="B50" t="n">
-        <v>39.16959381103516</v>
+        <v>34.95986557006836</v>
       </c>
       <c r="C50" t="n">
-        <v>-4.117749214172363</v>
+        <v>7.247988700866699</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1067343950271606</v>
+        <v>1.398774266242981</v>
       </c>
       <c r="E50" t="n">
-        <v>-5.481227397918701</v>
+        <v>-14.6407470703125</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.327541470527649</v>
+        <v>-15.96347427368164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>37.97940826416016</v>
+        <v>41.762939453125</v>
       </c>
       <c r="B51" t="n">
-        <v>40.71220397949219</v>
+        <v>36.4163932800293</v>
       </c>
       <c r="C51" t="n">
-        <v>-2.082728624343872</v>
+        <v>8.937695503234863</v>
       </c>
       <c r="D51" t="n">
-        <v>2.468558549880981</v>
+        <v>5.288212776184082</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.370247840881348</v>
+        <v>-15.28553199768066</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.52239990234375</v>
+        <v>-18.65155982971191</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>38.45115661621094</v>
+        <v>42.73750305175781</v>
       </c>
       <c r="B52" t="n">
-        <v>40.86177444458008</v>
+        <v>38.45062255859375</v>
       </c>
       <c r="C52" t="n">
-        <v>0.905834972858429</v>
+        <v>11.75856781005859</v>
       </c>
       <c r="D52" t="n">
-        <v>4.128376960754395</v>
+        <v>7.700995445251465</v>
       </c>
       <c r="E52" t="n">
-        <v>-9.373920440673828</v>
+        <v>-17.54406356811523</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.796849727630615</v>
+        <v>-19.38296508789062</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>38.35105895996094</v>
+        <v>43.8209114074707</v>
       </c>
       <c r="B53" t="n">
-        <v>41.11942672729492</v>
+        <v>39.57268524169922</v>
       </c>
       <c r="C53" t="n">
-        <v>2.781067609786987</v>
+        <v>15.23060131072998</v>
       </c>
       <c r="D53" t="n">
-        <v>6.54765796661377</v>
+        <v>11.92360973358154</v>
       </c>
       <c r="E53" t="n">
-        <v>-12.57905197143555</v>
+        <v>-17.90627288818359</v>
       </c>
       <c r="F53" t="n">
-        <v>-10.44286251068115</v>
+        <v>-21.33038330078125</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>38.00718307495117</v>
+        <v>43.27629089355469</v>
       </c>
       <c r="B54" t="n">
-        <v>41.68209075927734</v>
+        <v>40.32860946655273</v>
       </c>
       <c r="C54" t="n">
-        <v>4.868206977844238</v>
+        <v>18.42362594604492</v>
       </c>
       <c r="D54" t="n">
-        <v>9.105141639709473</v>
+        <v>14.99123287200928</v>
       </c>
       <c r="E54" t="n">
-        <v>-14.65743541717529</v>
+        <v>-19.49748992919922</v>
       </c>
       <c r="F54" t="n">
-        <v>-13.70405292510986</v>
+        <v>-22.60284233093262</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>37.12286376953125</v>
+        <v>42.80527496337891</v>
       </c>
       <c r="B55" t="n">
-        <v>41.90463638305664</v>
+        <v>39.67828369140625</v>
       </c>
       <c r="C55" t="n">
-        <v>7.106320381164551</v>
+        <v>21.88700294494629</v>
       </c>
       <c r="D55" t="n">
-        <v>12.07445335388184</v>
+        <v>17.20166969299316</v>
       </c>
       <c r="E55" t="n">
-        <v>-15.93590831756592</v>
+        <v>-19.13291931152344</v>
       </c>
       <c r="F55" t="n">
-        <v>-15.09282684326172</v>
+        <v>-23.60496139526367</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>35.91043090820312</v>
+        <v>41.89073181152344</v>
       </c>
       <c r="B56" t="n">
-        <v>41.15508270263672</v>
+        <v>38.34480285644531</v>
       </c>
       <c r="C56" t="n">
-        <v>8.514920234680176</v>
+        <v>23.52712249755859</v>
       </c>
       <c r="D56" t="n">
-        <v>14.72171497344971</v>
+        <v>19.3565502166748</v>
       </c>
       <c r="E56" t="n">
-        <v>-15.60564041137695</v>
+        <v>-16.79283142089844</v>
       </c>
       <c r="F56" t="n">
-        <v>-15.01501178741455</v>
+        <v>-23.4296989440918</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>34.67971801757812</v>
+        <v>39.61095428466797</v>
       </c>
       <c r="B57" t="n">
-        <v>40.21176147460938</v>
+        <v>35.93918228149414</v>
       </c>
       <c r="C57" t="n">
-        <v>9.853240013122559</v>
+        <v>25.10642051696777</v>
       </c>
       <c r="D57" t="n">
-        <v>17.4140682220459</v>
+        <v>19.98958969116211</v>
       </c>
       <c r="E57" t="n">
-        <v>-15.45810317993164</v>
+        <v>-14.723557472229</v>
       </c>
       <c r="F57" t="n">
-        <v>-13.98474216461182</v>
+        <v>-21.46813583374023</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>32.81666564941406</v>
+        <v>37.87957000732422</v>
       </c>
       <c r="B58" t="n">
-        <v>39.41963958740234</v>
+        <v>34.77781677246094</v>
       </c>
       <c r="C58" t="n">
-        <v>10.80666542053223</v>
+        <v>24.89349746704102</v>
       </c>
       <c r="D58" t="n">
-        <v>19.38233184814453</v>
+        <v>19.99852180480957</v>
       </c>
       <c r="E58" t="n">
-        <v>-11.80818176269531</v>
+        <v>-10.96758937835693</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.42349338531494</v>
+        <v>-18.15922355651855</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>31.14565849304199</v>
+        <v>35.37861251831055</v>
       </c>
       <c r="B59" t="n">
-        <v>37.92478942871094</v>
+        <v>32.25383758544922</v>
       </c>
       <c r="C59" t="n">
-        <v>11.4421558380127</v>
+        <v>23.84904479980469</v>
       </c>
       <c r="D59" t="n">
-        <v>20.47411727905273</v>
+        <v>20.00476264953613</v>
       </c>
       <c r="E59" t="n">
-        <v>-8.175715446472168</v>
+        <v>-6.820231914520264</v>
       </c>
       <c r="F59" t="n">
-        <v>-6.427661418914795</v>
+        <v>-14.11149215698242</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>29.40776824951172</v>
+        <v>32.779296875</v>
       </c>
       <c r="B60" t="n">
-        <v>35.57950592041016</v>
+        <v>29.00386047363281</v>
       </c>
       <c r="C60" t="n">
-        <v>11.64324378967285</v>
+        <v>22.67152976989746</v>
       </c>
       <c r="D60" t="n">
-        <v>21.11513710021973</v>
+        <v>17.90555191040039</v>
       </c>
       <c r="E60" t="n">
-        <v>-5.214907646179199</v>
+        <v>-3.259596347808838</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.118530750274658</v>
+        <v>-12.22720623016357</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>27.55718231201172</v>
+        <v>30.27034568786621</v>
       </c>
       <c r="B61" t="n">
-        <v>33.71977233886719</v>
+        <v>25.18896102905273</v>
       </c>
       <c r="C61" t="n">
-        <v>11.23771190643311</v>
+        <v>20.60074806213379</v>
       </c>
       <c r="D61" t="n">
-        <v>20.7260913848877</v>
+        <v>15.80327224731445</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.49940013885498</v>
+        <v>-0.8952131271362305</v>
       </c>
       <c r="F61" t="n">
-        <v>1.009332060813904</v>
+        <v>-8.890900611877441</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>24.95822906494141</v>
+        <v>26.97348594665527</v>
       </c>
       <c r="B62" t="n">
-        <v>31.53730201721191</v>
+        <v>22.1519832611084</v>
       </c>
       <c r="C62" t="n">
-        <v>10.77876281738281</v>
+        <v>17.90589714050293</v>
       </c>
       <c r="D62" t="n">
-        <v>19.91916084289551</v>
+        <v>13.48603916168213</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.400693416595459</v>
+        <v>1.287602424621582</v>
       </c>
       <c r="F62" t="n">
-        <v>3.601325988769531</v>
+        <v>-7.011600017547607</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>22.99932479858398</v>
+        <v>23.39443588256836</v>
       </c>
       <c r="B63" t="n">
-        <v>28.75641059875488</v>
+        <v>19.54497528076172</v>
       </c>
       <c r="C63" t="n">
-        <v>9.874597549438477</v>
+        <v>15.60567665100098</v>
       </c>
       <c r="D63" t="n">
-        <v>18.72232055664062</v>
+        <v>10.86274814605713</v>
       </c>
       <c r="E63" t="n">
-        <v>1.55504035949707</v>
+        <v>2.180611610412598</v>
       </c>
       <c r="F63" t="n">
-        <v>5.336904525756836</v>
+        <v>-5.861984252929688</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20.68378829956055</v>
+        <v>20.47353744506836</v>
       </c>
       <c r="B64" t="n">
-        <v>26.5877742767334</v>
+        <v>15.62396621704102</v>
       </c>
       <c r="C64" t="n">
-        <v>8.799025535583496</v>
+        <v>12.24829959869385</v>
       </c>
       <c r="D64" t="n">
-        <v>17.52611541748047</v>
+        <v>9.181735038757324</v>
       </c>
       <c r="E64" t="n">
-        <v>3.041244506835938</v>
+        <v>3.445561408996582</v>
       </c>
       <c r="F64" t="n">
-        <v>7.741361618041992</v>
+        <v>-4.340884685516357</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>18.75373458862305</v>
+        <v>17.65938568115234</v>
       </c>
       <c r="B65" t="n">
-        <v>24.1822509765625</v>
+        <v>12.9914436340332</v>
       </c>
       <c r="C65" t="n">
-        <v>7.93904972076416</v>
+        <v>10.31638050079346</v>
       </c>
       <c r="D65" t="n">
-        <v>16.82439041137695</v>
+        <v>6.479107856750488</v>
       </c>
       <c r="E65" t="n">
-        <v>4.973950386047363</v>
+        <v>4.812032699584961</v>
       </c>
       <c r="F65" t="n">
-        <v>9.193641662597656</v>
+        <v>-2.891557455062866</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>16.44602966308594</v>
+        <v>14.38814544677734</v>
       </c>
       <c r="B66" t="n">
-        <v>21.62963676452637</v>
+        <v>9.707518577575684</v>
       </c>
       <c r="C66" t="n">
-        <v>7.060917854309082</v>
+        <v>9.042622566223145</v>
       </c>
       <c r="D66" t="n">
-        <v>15.27888584136963</v>
+        <v>5.489001274108887</v>
       </c>
       <c r="E66" t="n">
-        <v>6.683996200561523</v>
+        <v>5.558104515075684</v>
       </c>
       <c r="F66" t="n">
-        <v>10.74170112609863</v>
+        <v>-1.083420872688293</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>14.8505277633667</v>
+        <v>11.40669059753418</v>
       </c>
       <c r="B67" t="n">
-        <v>19.55872344970703</v>
+        <v>6.720000267028809</v>
       </c>
       <c r="C67" t="n">
-        <v>6.323365211486816</v>
+        <v>6.314009666442871</v>
       </c>
       <c r="D67" t="n">
-        <v>14.36285305023193</v>
+        <v>4.360884666442871</v>
       </c>
       <c r="E67" t="n">
-        <v>8.501965522766113</v>
+        <v>7.180859565734863</v>
       </c>
       <c r="F67" t="n">
-        <v>12.53233909606934</v>
+        <v>2.807138442993164</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>12.64598369598389</v>
+        <v>8.69875431060791</v>
       </c>
       <c r="B68" t="n">
-        <v>17.19081687927246</v>
+        <v>4.025485038757324</v>
       </c>
       <c r="C68" t="n">
-        <v>5.542180061340332</v>
+        <v>5.490229606628418</v>
       </c>
       <c r="D68" t="n">
-        <v>12.9413480758667</v>
+        <v>3.8093101978302</v>
       </c>
       <c r="E68" t="n">
-        <v>9.885684013366699</v>
+        <v>9.29830265045166</v>
       </c>
       <c r="F68" t="n">
-        <v>13.89080429077148</v>
+        <v>5.273722648620605</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>11.2311315536499</v>
+        <v>5.93093729019165</v>
       </c>
       <c r="B69" t="n">
-        <v>15.28518867492676</v>
+        <v>1.753760099411011</v>
       </c>
       <c r="C69" t="n">
-        <v>4.928183555603027</v>
+        <v>4.81214427947998</v>
       </c>
       <c r="D69" t="n">
-        <v>12.63430595397949</v>
+        <v>4.127816200256348</v>
       </c>
       <c r="E69" t="n">
-        <v>12.10934734344482</v>
+        <v>11.71322917938232</v>
       </c>
       <c r="F69" t="n">
-        <v>16.06899452209473</v>
+        <v>7.670042991638184</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>9.32944393157959</v>
+        <v>3.642683506011963</v>
       </c>
       <c r="B70" t="n">
-        <v>13.49625015258789</v>
+        <v>-0.6221668124198914</v>
       </c>
       <c r="C70" t="n">
-        <v>4.562254905700684</v>
+        <v>4.583470344543457</v>
       </c>
       <c r="D70" t="n">
-        <v>11.88622665405273</v>
+        <v>2.517668962478638</v>
       </c>
       <c r="E70" t="n">
-        <v>13.99587535858154</v>
+        <v>14.16074085235596</v>
       </c>
       <c r="F70" t="n">
-        <v>18.36870574951172</v>
+        <v>10.48445701599121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>8.00676441192627</v>
+        <v>0.8145433068275452</v>
       </c>
       <c r="B71" t="n">
-        <v>12.1861572265625</v>
+        <v>-4.24828052520752</v>
       </c>
       <c r="C71" t="n">
-        <v>4.901036262512207</v>
+        <v>5.011494636535645</v>
       </c>
       <c r="D71" t="n">
-        <v>12.09523868560791</v>
+        <v>3.030267000198364</v>
       </c>
       <c r="E71" t="n">
-        <v>15.13865184783936</v>
+        <v>17.49827194213867</v>
       </c>
       <c r="F71" t="n">
-        <v>20.89568710327148</v>
+        <v>13.41130065917969</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6.398899555206299</v>
+        <v>-0.03640121221542358</v>
       </c>
       <c r="B72" t="n">
-        <v>11.16428470611572</v>
+        <v>-6.083085060119629</v>
       </c>
       <c r="C72" t="n">
-        <v>5.634276390075684</v>
+        <v>5.908583641052246</v>
       </c>
       <c r="D72" t="n">
-        <v>12.63421535491943</v>
+        <v>3.80071759223938</v>
       </c>
       <c r="E72" t="n">
-        <v>16.59846305847168</v>
+        <v>20.73954582214355</v>
       </c>
       <c r="F72" t="n">
-        <v>23.78654861450195</v>
+        <v>15.69699668884277</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4.839371204376221</v>
+        <v>-1.236922740936279</v>
       </c>
       <c r="B73" t="n">
-        <v>10.18016529083252</v>
+        <v>-8.107542991638184</v>
       </c>
       <c r="C73" t="n">
-        <v>6.805573463439941</v>
+        <v>6.681904792785645</v>
       </c>
       <c r="D73" t="n">
-        <v>13.14418506622314</v>
+        <v>4.324681282043457</v>
       </c>
       <c r="E73" t="n">
-        <v>17.09641647338867</v>
+        <v>21.50927734375</v>
       </c>
       <c r="F73" t="n">
-        <v>25.84319877624512</v>
+        <v>17.57651710510254</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3.604912281036377</v>
+        <v>-2.710568904876709</v>
       </c>
       <c r="B74" t="n">
-        <v>9.1934814453125</v>
+        <v>-10.63731288909912</v>
       </c>
       <c r="C74" t="n">
-        <v>8.071026802062988</v>
+        <v>8.230313301086426</v>
       </c>
       <c r="D74" t="n">
-        <v>14.64622020721436</v>
+        <v>6.151337623596191</v>
       </c>
       <c r="E74" t="n">
-        <v>17.35044288635254</v>
+        <v>22.30587577819824</v>
       </c>
       <c r="F74" t="n">
-        <v>28.24874687194824</v>
+        <v>17.84346199035645</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3.050055027008057</v>
+        <v>-3.918714046478271</v>
       </c>
       <c r="B75" t="n">
-        <v>7.566304206848145</v>
+        <v>-12.21414470672607</v>
       </c>
       <c r="C75" t="n">
-        <v>9.082327842712402</v>
+        <v>11.59996318817139</v>
       </c>
       <c r="D75" t="n">
-        <v>15.56231212615967</v>
+        <v>7.534773826599121</v>
       </c>
       <c r="E75" t="n">
-        <v>16.97235679626465</v>
+        <v>22.14043045043945</v>
       </c>
       <c r="F75" t="n">
-        <v>29.96687507629395</v>
+        <v>16.76305961608887</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1.499321460723877</v>
+        <v>-4.087684154510498</v>
       </c>
       <c r="B76" t="n">
-        <v>6.611330986022949</v>
+        <v>-12.68188381195068</v>
       </c>
       <c r="C76" t="n">
-        <v>11.26136779785156</v>
+        <v>14.87400531768799</v>
       </c>
       <c r="D76" t="n">
-        <v>17.15046691894531</v>
+        <v>9.922890663146973</v>
       </c>
       <c r="E76" t="n">
-        <v>15.12979221343994</v>
+        <v>17.56279182434082</v>
       </c>
       <c r="F76" t="n">
-        <v>31.02389717102051</v>
+        <v>13.41831398010254</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.7194982171058655</v>
+        <v>-3.323789119720459</v>
       </c>
       <c r="B77" t="n">
-        <v>5.118866920471191</v>
+        <v>-12.35597515106201</v>
       </c>
       <c r="C77" t="n">
-        <v>13.68700885772705</v>
+        <v>19.20474624633789</v>
       </c>
       <c r="D77" t="n">
-        <v>19.03923416137695</v>
+        <v>13.23991584777832</v>
       </c>
       <c r="E77" t="n">
-        <v>10.02903270721436</v>
+        <v>10.29619312286377</v>
       </c>
       <c r="F77" t="n">
-        <v>29.44741630554199</v>
+        <v>7.551743507385254</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.3145967125892639</v>
+        <v>-2.587483882904053</v>
       </c>
       <c r="B78" t="n">
-        <v>4.309657096862793</v>
+        <v>-12.704665184021</v>
       </c>
       <c r="C78" t="n">
-        <v>16.70339965820312</v>
+        <v>24.64759063720703</v>
       </c>
       <c r="D78" t="n">
-        <v>21.81219291687012</v>
+        <v>17.21047401428223</v>
       </c>
       <c r="E78" t="n">
-        <v>2.926568031311035</v>
+        <v>1.034248352050781</v>
       </c>
       <c r="F78" t="n">
-        <v>25.3050422668457</v>
+        <v>0.008509093895554543</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.2311292290687561</v>
+        <v>-1.156945705413818</v>
       </c>
       <c r="B79" t="n">
-        <v>4.190888404846191</v>
+        <v>-11.58913326263428</v>
       </c>
       <c r="C79" t="n">
-        <v>20.51653099060059</v>
+        <v>30.14649772644043</v>
       </c>
       <c r="D79" t="n">
-        <v>25.42946434020996</v>
+        <v>23.0304012298584</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.372158050537109</v>
+        <v>-11.18795490264893</v>
       </c>
       <c r="F79" t="n">
-        <v>18.3952808380127</v>
+        <v>-8.456538200378418</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1.958912372589111</v>
+        <v>0.5117974877357483</v>
       </c>
       <c r="B80" t="n">
-        <v>3.94490122795105</v>
+        <v>-9.789229393005371</v>
       </c>
       <c r="C80" t="n">
-        <v>25.87648582458496</v>
+        <v>36.50432205200195</v>
       </c>
       <c r="D80" t="n">
-        <v>29.60067749023438</v>
+        <v>27.89463233947754</v>
       </c>
       <c r="E80" t="n">
-        <v>-19.70647239685059</v>
+        <v>-22.49267768859863</v>
       </c>
       <c r="F80" t="n">
-        <v>7.068784713745117</v>
+        <v>-17.83271980285645</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3.440376758575439</v>
+        <v>2.787662982940674</v>
       </c>
       <c r="B81" t="n">
-        <v>5.339238166809082</v>
+        <v>-6.830605506896973</v>
       </c>
       <c r="C81" t="n">
-        <v>32.15237426757812</v>
+        <v>43.16443634033203</v>
       </c>
       <c r="D81" t="n">
-        <v>35.67501068115234</v>
+        <v>34.25237655639648</v>
       </c>
       <c r="E81" t="n">
-        <v>-31.63046073913574</v>
+        <v>-32.06926345825195</v>
       </c>
       <c r="F81" t="n">
-        <v>-5.44465446472168</v>
+        <v>-25.26853942871094</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5.800814151763916</v>
+        <v>6.372393131256104</v>
       </c>
       <c r="B82" t="n">
-        <v>8.00944709777832</v>
+        <v>-3.926203966140747</v>
       </c>
       <c r="C82" t="n">
-        <v>38.07534027099609</v>
+        <v>48.84598159790039</v>
       </c>
       <c r="D82" t="n">
-        <v>42.70425796508789</v>
+        <v>40.44765090942383</v>
       </c>
       <c r="E82" t="n">
-        <v>-40.45498275756836</v>
+        <v>-38.45978927612305</v>
       </c>
       <c r="F82" t="n">
-        <v>-17.88174629211426</v>
+        <v>-31.81167030334473</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>9.3614501953125</v>
+        <v>10.56767559051514</v>
       </c>
       <c r="B83" t="n">
-        <v>10.69480609893799</v>
+        <v>-0.2163516879081726</v>
       </c>
       <c r="C83" t="n">
-        <v>44.47929000854492</v>
+        <v>55.34775161743164</v>
       </c>
       <c r="D83" t="n">
-        <v>49.01173782348633</v>
+        <v>46.96779632568359</v>
       </c>
       <c r="E83" t="n">
-        <v>-43.4840087890625</v>
+        <v>-40.85408401489258</v>
       </c>
       <c r="F83" t="n">
-        <v>-26.84637260437012</v>
+        <v>-32.97284698486328</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>13.29438781738281</v>
+        <v>14.22406959533691</v>
       </c>
       <c r="B84" t="n">
-        <v>14.07547855377197</v>
+        <v>4.360775947570801</v>
       </c>
       <c r="C84" t="n">
-        <v>49.54402542114258</v>
+        <v>60.83193206787109</v>
       </c>
       <c r="D84" t="n">
-        <v>54.72346878051758</v>
+        <v>52.34833526611328</v>
       </c>
       <c r="E84" t="n">
-        <v>-41.04464340209961</v>
+        <v>-39.78069305419922</v>
       </c>
       <c r="F84" t="n">
-        <v>-31.03660583496094</v>
+        <v>-32.24224472045898</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>16.74869155883789</v>
+        <v>17.93943786621094</v>
       </c>
       <c r="B85" t="n">
-        <v>17.88338661193848</v>
+        <v>8.628585815429688</v>
       </c>
       <c r="C85" t="n">
-        <v>52.93581771850586</v>
+        <v>65.39506530761719</v>
       </c>
       <c r="D85" t="n">
-        <v>59.913818359375</v>
+        <v>57.4937629699707</v>
       </c>
       <c r="E85" t="n">
-        <v>-33.77459716796875</v>
+        <v>-34.04836654663086</v>
       </c>
       <c r="F85" t="n">
-        <v>-29.91612815856934</v>
+        <v>-29.20149230957031</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>20.06715202331543</v>
+        <v>22.94804573059082</v>
       </c>
       <c r="B86" t="n">
-        <v>21.52153205871582</v>
+        <v>12.75113296508789</v>
       </c>
       <c r="C86" t="n">
-        <v>54.00663757324219</v>
+        <v>68.43352508544922</v>
       </c>
       <c r="D86" t="n">
-        <v>62.03565979003906</v>
+        <v>58.84362030029297</v>
       </c>
       <c r="E86" t="n">
-        <v>-24.01735496520996</v>
+        <v>-26.30283546447754</v>
       </c>
       <c r="F86" t="n">
-        <v>-24.9088134765625</v>
+        <v>-24.37583351135254</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>23.47247886657715</v>
+        <v>26.05851173400879</v>
       </c>
       <c r="B87" t="n">
-        <v>24.79911422729492</v>
+        <v>17.2607421875</v>
       </c>
       <c r="C87" t="n">
-        <v>53.98670959472656</v>
+        <v>67.85497283935547</v>
       </c>
       <c r="D87" t="n">
-        <v>63.31955718994141</v>
+        <v>61.4716796875</v>
       </c>
       <c r="E87" t="n">
-        <v>-14.43675899505615</v>
+        <v>-18.30361175537109</v>
       </c>
       <c r="F87" t="n">
-        <v>-17.20365142822266</v>
+        <v>-17.95368003845215</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>25.99045753479004</v>
+        <v>29.63801574707031</v>
       </c>
       <c r="B88" t="n">
-        <v>28.22663307189941</v>
+        <v>21.36712646484375</v>
       </c>
       <c r="C88" t="n">
-        <v>50.37397003173828</v>
+        <v>66.8514404296875</v>
       </c>
       <c r="D88" t="n">
-        <v>60.97175598144531</v>
+        <v>60.61903381347656</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.013108730316162</v>
+        <v>-11.09215450286865</v>
       </c>
       <c r="F88" t="n">
-        <v>-9.68324089050293</v>
+        <v>-10.95928287506104</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>28.18152618408203</v>
+        <v>32.22859954833984</v>
       </c>
       <c r="B89" t="n">
-        <v>30.95845222473145</v>
+        <v>24.46733093261719</v>
       </c>
       <c r="C89" t="n">
-        <v>46.76353454589844</v>
+        <v>63.6415901184082</v>
       </c>
       <c r="D89" t="n">
-        <v>58.36732482910156</v>
+        <v>57.90721893310547</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.83217191696167</v>
+        <v>-5.485466480255127</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.579062223434448</v>
+        <v>-7.454801082611084</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>30.30741691589355</v>
+        <v>34.34187316894531</v>
       </c>
       <c r="B90" t="n">
-        <v>33.10227584838867</v>
+        <v>27.07218933105469</v>
       </c>
       <c r="C90" t="n">
-        <v>40.21484375</v>
+        <v>57.89492416381836</v>
       </c>
       <c r="D90" t="n">
-        <v>53.73043823242188</v>
+        <v>54.22291946411133</v>
       </c>
       <c r="E90" t="n">
-        <v>1.328511238098145</v>
+        <v>-3.146072387695312</v>
       </c>
       <c r="F90" t="n">
-        <v>2.635266304016113</v>
+        <v>-4.396828651428223</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>31.78849029541016</v>
+        <v>35.43340301513672</v>
       </c>
       <c r="B91" t="n">
-        <v>36.01447296142578</v>
+        <v>28.73242950439453</v>
       </c>
       <c r="C91" t="n">
-        <v>33.99325180053711</v>
+        <v>51.21190643310547</v>
       </c>
       <c r="D91" t="n">
-        <v>48.58818435668945</v>
+        <v>47.49718856811523</v>
       </c>
       <c r="E91" t="n">
-        <v>2.499344825744629</v>
+        <v>-2.148545742034912</v>
       </c>
       <c r="F91" t="n">
-        <v>6.325119018554688</v>
+        <v>-2.640106439590454</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>32.9030876159668</v>
+        <v>36.36133575439453</v>
       </c>
       <c r="B92" t="n">
-        <v>37.39562225341797</v>
+        <v>30.28422737121582</v>
       </c>
       <c r="C92" t="n">
-        <v>27.48737525939941</v>
+        <v>42.82732772827148</v>
       </c>
       <c r="D92" t="n">
-        <v>41.90373992919922</v>
+        <v>40.44596481323242</v>
       </c>
       <c r="E92" t="n">
-        <v>2.667838096618652</v>
+        <v>-3.359604835510254</v>
       </c>
       <c r="F92" t="n">
-        <v>7.494237899780273</v>
+        <v>-2.908233642578125</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>33.79678726196289</v>
+        <v>36.25750350952148</v>
       </c>
       <c r="B93" t="n">
-        <v>38.61548233032227</v>
+        <v>31.50735473632812</v>
       </c>
       <c r="C93" t="n">
-        <v>20.23866844177246</v>
+        <v>34.64248657226562</v>
       </c>
       <c r="D93" t="n">
-        <v>34.13401412963867</v>
+        <v>31.59437561035156</v>
       </c>
       <c r="E93" t="n">
-        <v>1.797555923461914</v>
+        <v>-4.195308685302734</v>
       </c>
       <c r="F93" t="n">
-        <v>7.594221115112305</v>
+        <v>-4.207176208496094</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>34.29188537597656</v>
+        <v>37.19440460205078</v>
       </c>
       <c r="B94" t="n">
-        <v>39.27055740356445</v>
+        <v>31.62080383300781</v>
       </c>
       <c r="C94" t="n">
-        <v>12.82565307617188</v>
+        <v>26.75216865539551</v>
       </c>
       <c r="D94" t="n">
-        <v>26.87050819396973</v>
+        <v>24.50613975524902</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8746404647827148</v>
+        <v>-7.178625106811523</v>
       </c>
       <c r="F94" t="n">
-        <v>5.857996940612793</v>
+        <v>-6.904961585998535</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>35.34376525878906</v>
+        <v>36.8797721862793</v>
       </c>
       <c r="B95" t="n">
-        <v>39.80244445800781</v>
+        <v>32.04653167724609</v>
       </c>
       <c r="C95" t="n">
-        <v>5.843077659606934</v>
+        <v>18.6003475189209</v>
       </c>
       <c r="D95" t="n">
-        <v>19.20870971679688</v>
+        <v>16.74412727355957</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.4621572494506836</v>
+        <v>-9.291399002075195</v>
       </c>
       <c r="F95" t="n">
-        <v>4.06369686126709</v>
+        <v>-8.952938079833984</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>35.31443405151367</v>
+        <v>36.40034484863281</v>
       </c>
       <c r="B96" t="n">
-        <v>39.84391021728516</v>
+        <v>31.84616851806641</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2942913174629211</v>
+        <v>12.47576522827148</v>
       </c>
       <c r="D96" t="n">
-        <v>11.81530570983887</v>
+        <v>9.936263084411621</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.6570367813110352</v>
+        <v>-10.40364265441895</v>
       </c>
       <c r="F96" t="n">
-        <v>2.522146224975586</v>
+        <v>-10.44585609436035</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>35.9820671081543</v>
+        <v>36.55059051513672</v>
       </c>
       <c r="B97" t="n">
-        <v>39.73508453369141</v>
+        <v>31.82938003540039</v>
       </c>
       <c r="C97" t="n">
-        <v>-4.030755043029785</v>
+        <v>8.208504676818848</v>
       </c>
       <c r="D97" t="n">
-        <v>5.061572074890137</v>
+        <v>4.983523368835449</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.07744026184082</v>
+        <v>-12.30721855163574</v>
       </c>
       <c r="F97" t="n">
-        <v>1.300980925559998</v>
+        <v>-12.97388744354248</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>36.42602920532227</v>
+        <v>36.35356903076172</v>
       </c>
       <c r="B98" t="n">
-        <v>39.54217529296875</v>
+        <v>32.24713134765625</v>
       </c>
       <c r="C98" t="n">
-        <v>-6.293267250061035</v>
+        <v>5.89908504486084</v>
       </c>
       <c r="D98" t="n">
-        <v>1.594468235969543</v>
+        <v>1.382231831550598</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.479525089263916</v>
+        <v>-13.03630256652832</v>
       </c>
       <c r="F98" t="n">
-        <v>1.112107634544373</v>
+        <v>-14.06296157836914</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>37.14525604248047</v>
+        <v>36.84664535522461</v>
       </c>
       <c r="B99" t="n">
-        <v>39.3635368347168</v>
+        <v>32.38263702392578</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.403731346130371</v>
+        <v>4.974991798400879</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.82500159740448</v>
+        <v>0.6666899919509888</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.553321361541748</v>
+        <v>-13.61758327484131</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9042624831199646</v>
+        <v>-15.48391819000244</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>37.42211151123047</v>
+        <v>38.9428825378418</v>
       </c>
       <c r="B100" t="n">
-        <v>39.23434829711914</v>
+        <v>33.24254989624023</v>
       </c>
       <c r="C100" t="n">
-        <v>-6.494956016540527</v>
+        <v>4.880059242248535</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.9672077894210815</v>
+        <v>0.3089534044265747</v>
       </c>
       <c r="E100" t="n">
-        <v>-3.253890514373779</v>
+        <v>-14.12606239318848</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.3562145829200745</v>
+        <v>-16.24225234985352</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>38.10757064819336</v>
+        <v>41.01066970825195</v>
       </c>
       <c r="B101" t="n">
-        <v>39.17527770996094</v>
+        <v>35.15885162353516</v>
       </c>
       <c r="C101" t="n">
-        <v>-4.28707218170166</v>
+        <v>6.958752632141113</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.1113899946212769</v>
+        <v>1.367430806159973</v>
       </c>
       <c r="E101" t="n">
-        <v>-5.336749076843262</v>
+        <v>-15.13297176361084</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.73691999912262</v>
+        <v>-16.29285621643066</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>38.04620742797852</v>
+        <v>41.68521881103516</v>
       </c>
       <c r="B102" t="n">
-        <v>40.49798583984375</v>
+        <v>36.7403678894043</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.931153416633606</v>
+        <v>9.117773056030273</v>
       </c>
       <c r="D102" t="n">
-        <v>2.181065797805786</v>
+        <v>5.15516185760498</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.376756191253662</v>
+        <v>-15.74498176574707</v>
       </c>
       <c r="F102" t="n">
-        <v>-3.869811296463013</v>
+        <v>-18.64070510864258</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>38.44155502319336</v>
+        <v>42.88697814941406</v>
       </c>
       <c r="B103" t="n">
-        <v>40.7436637878418</v>
+        <v>38.75783157348633</v>
       </c>
       <c r="C103" t="n">
-        <v>0.9376304745674133</v>
+        <v>11.86942386627197</v>
       </c>
       <c r="D103" t="n">
-        <v>4.072968482971191</v>
+        <v>7.967902183532715</v>
       </c>
       <c r="E103" t="n">
-        <v>-9.530084609985352</v>
+        <v>-18.00148963928223</v>
       </c>
       <c r="F103" t="n">
-        <v>-7.015275955200195</v>
+        <v>-19.3820858001709</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>38.34285736083984</v>
+        <v>43.83863830566406</v>
       </c>
       <c r="B104" t="n">
-        <v>41.11381912231445</v>
+        <v>39.74298477172852</v>
       </c>
       <c r="C104" t="n">
-        <v>2.730889081954956</v>
+        <v>15.22974109649658</v>
       </c>
       <c r="D104" t="n">
-        <v>6.469910621643066</v>
+        <v>11.83112239837646</v>
       </c>
       <c r="E104" t="n">
-        <v>-12.5843677520752</v>
+        <v>-18.15242385864258</v>
       </c>
       <c r="F104" t="n">
-        <v>-10.50131034851074</v>
+        <v>-21.32385444641113</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>38.00016784667969</v>
+        <v>43.23220825195312</v>
       </c>
       <c r="B105" t="n">
-        <v>41.6312370300293</v>
+        <v>40.41677093505859</v>
       </c>
       <c r="C105" t="n">
-        <v>4.820096015930176</v>
+        <v>18.50432205200195</v>
       </c>
       <c r="D105" t="n">
-        <v>9.045966148376465</v>
+        <v>14.91316795349121</v>
       </c>
       <c r="E105" t="n">
-        <v>-14.64985370635986</v>
+        <v>-19.50855255126953</v>
       </c>
       <c r="F105" t="n">
-        <v>-13.69046783447266</v>
+        <v>-22.5156307220459</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>37.11035919189453</v>
+        <v>42.87627029418945</v>
       </c>
       <c r="B106" t="n">
-        <v>41.82009887695312</v>
+        <v>39.8062858581543</v>
       </c>
       <c r="C106" t="n">
-        <v>7.07155704498291</v>
+        <v>21.80558013916016</v>
       </c>
       <c r="D106" t="n">
-        <v>11.97188472747803</v>
+        <v>17.20296669006348</v>
       </c>
       <c r="E106" t="n">
-        <v>-15.90939235687256</v>
+        <v>-19.13351058959961</v>
       </c>
       <c r="F106" t="n">
-        <v>-15.02393245697021</v>
+        <v>-23.50498390197754</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>35.86473846435547</v>
+        <v>42.04476165771484</v>
       </c>
       <c r="B107" t="n">
-        <v>41.10952758789062</v>
+        <v>38.5669059753418</v>
       </c>
       <c r="C107" t="n">
-        <v>8.526673316955566</v>
+        <v>23.57032203674316</v>
       </c>
       <c r="D107" t="n">
-        <v>14.67860317230225</v>
+        <v>19.27774238586426</v>
       </c>
       <c r="E107" t="n">
-        <v>-15.6121072769165</v>
+        <v>-16.83953285217285</v>
       </c>
       <c r="F107" t="n">
-        <v>-14.93097496032715</v>
+        <v>-23.22867774963379</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>34.66300964355469</v>
+        <v>39.7563362121582</v>
       </c>
       <c r="B108" t="n">
-        <v>40.13864135742188</v>
+        <v>36.15513229370117</v>
       </c>
       <c r="C108" t="n">
-        <v>9.852686882019043</v>
+        <v>25.09555053710938</v>
       </c>
       <c r="D108" t="n">
-        <v>17.38263893127441</v>
+        <v>19.87467765808105</v>
       </c>
       <c r="E108" t="n">
-        <v>-15.41856861114502</v>
+        <v>-14.74702262878418</v>
       </c>
       <c r="F108" t="n">
-        <v>-13.89098453521729</v>
+        <v>-21.35305595397949</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>32.80878829956055</v>
+        <v>37.99260711669922</v>
       </c>
       <c r="B109" t="n">
-        <v>39.34230041503906</v>
+        <v>34.87044906616211</v>
       </c>
       <c r="C109" t="n">
-        <v>10.82873725891113</v>
+        <v>25.00729370117188</v>
       </c>
       <c r="D109" t="n">
-        <v>19.3608455657959</v>
+        <v>19.86566734313965</v>
       </c>
       <c r="E109" t="n">
-        <v>-11.79124546051025</v>
+        <v>-11.04245853424072</v>
       </c>
       <c r="F109" t="n">
-        <v>-10.33583354949951</v>
+        <v>-18.14349555969238</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>31.11362648010254</v>
+        <v>35.48452377319336</v>
       </c>
       <c r="B110" t="n">
-        <v>37.86988830566406</v>
+        <v>32.39719390869141</v>
       </c>
       <c r="C110" t="n">
-        <v>11.40462017059326</v>
+        <v>23.87132453918457</v>
       </c>
       <c r="D110" t="n">
-        <v>20.44473838806152</v>
+        <v>19.78428268432617</v>
       </c>
       <c r="E110" t="n">
-        <v>-8.152667045593262</v>
+        <v>-6.841246604919434</v>
       </c>
       <c r="F110" t="n">
-        <v>-6.33290433883667</v>
+        <v>-14.16367435455322</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>29.39432144165039</v>
+        <v>32.94269180297852</v>
       </c>
       <c r="B111" t="n">
-        <v>35.5172119140625</v>
+        <v>29.08122825622559</v>
       </c>
       <c r="C111" t="n">
-        <v>11.60437774658203</v>
+        <v>22.62087440490723</v>
       </c>
       <c r="D111" t="n">
-        <v>21.10395622253418</v>
+        <v>17.69708633422852</v>
       </c>
       <c r="E111" t="n">
-        <v>-5.21896505355835</v>
+        <v>-3.354323863983154</v>
       </c>
       <c r="F111" t="n">
-        <v>-2.041983127593994</v>
+        <v>-12.1995792388916</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>27.52218627929688</v>
+        <v>30.37433624267578</v>
       </c>
       <c r="B112" t="n">
-        <v>33.65298843383789</v>
+        <v>25.34355163574219</v>
       </c>
       <c r="C112" t="n">
-        <v>11.17931175231934</v>
+        <v>20.56417274475098</v>
       </c>
       <c r="D112" t="n">
-        <v>20.64989852905273</v>
+        <v>15.74837207794189</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.494794845581055</v>
+        <v>-0.9547538757324219</v>
       </c>
       <c r="F112" t="n">
-        <v>1.060060858726501</v>
+        <v>-9.014529228210449</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>24.95180320739746</v>
+        <v>27.13256072998047</v>
       </c>
       <c r="B113" t="n">
-        <v>31.50101470947266</v>
+        <v>22.27413749694824</v>
       </c>
       <c r="C113" t="n">
-        <v>10.73818016052246</v>
+        <v>17.90726089477539</v>
       </c>
       <c r="D113" t="n">
-        <v>19.90966606140137</v>
+        <v>13.35217571258545</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.391108512878418</v>
+        <v>1.22676944732666</v>
       </c>
       <c r="F113" t="n">
-        <v>3.683026313781738</v>
+        <v>-7.058507442474365</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>22.95915031433105</v>
+        <v>23.51772689819336</v>
       </c>
       <c r="B114" t="n">
-        <v>28.72879219055176</v>
+        <v>19.64639663696289</v>
       </c>
       <c r="C114" t="n">
-        <v>9.830760955810547</v>
+        <v>15.60173320770264</v>
       </c>
       <c r="D114" t="n">
-        <v>18.69190406799316</v>
+        <v>10.78756904602051</v>
       </c>
       <c r="E114" t="n">
-        <v>1.539042472839355</v>
+        <v>2.26016902923584</v>
       </c>
       <c r="F114" t="n">
-        <v>5.405614852905273</v>
+        <v>-5.923821926116943</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>20.66235733032227</v>
+        <v>20.54423522949219</v>
       </c>
       <c r="B115" t="n">
-        <v>26.58311080932617</v>
+        <v>15.72672843933105</v>
       </c>
       <c r="C115" t="n">
-        <v>8.727189064025879</v>
+        <v>12.33359050750732</v>
       </c>
       <c r="D115" t="n">
-        <v>17.49960327148438</v>
+        <v>8.982935905456543</v>
       </c>
       <c r="E115" t="n">
-        <v>3.001413345336914</v>
+        <v>3.523185729980469</v>
       </c>
       <c r="F115" t="n">
-        <v>7.801688194274902</v>
+        <v>-4.340766429901123</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>18.73615455627441</v>
+        <v>17.70422554016113</v>
       </c>
       <c r="B116" t="n">
-        <v>24.18670463562012</v>
+        <v>13.02234077453613</v>
       </c>
       <c r="C116" t="n">
-        <v>7.854743003845215</v>
+        <v>10.24036598205566</v>
       </c>
       <c r="D116" t="n">
-        <v>16.81506538391113</v>
+        <v>6.443072319030762</v>
       </c>
       <c r="E116" t="n">
-        <v>4.910580635070801</v>
+        <v>4.779962539672852</v>
       </c>
       <c r="F116" t="n">
-        <v>9.284018516540527</v>
+        <v>-2.841959714889526</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>16.40915679931641</v>
+        <v>14.47510623931885</v>
       </c>
       <c r="B117" t="n">
-        <v>21.61128807067871</v>
+        <v>9.749518394470215</v>
       </c>
       <c r="C117" t="n">
-        <v>6.95671558380127</v>
+        <v>8.946091651916504</v>
       </c>
       <c r="D117" t="n">
-        <v>15.22052478790283</v>
+        <v>5.401701927185059</v>
       </c>
       <c r="E117" t="n">
-        <v>6.615211486816406</v>
+        <v>5.578522682189941</v>
       </c>
       <c r="F117" t="n">
-        <v>10.78531455993652</v>
+        <v>-0.9035034775733948</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>14.814772605896</v>
+        <v>11.52645206451416</v>
       </c>
       <c r="B118" t="n">
-        <v>19.54371643066406</v>
+        <v>6.78455638885498</v>
       </c>
       <c r="C118" t="n">
-        <v>6.230521202087402</v>
+        <v>6.308714866638184</v>
       </c>
       <c r="D118" t="n">
-        <v>14.3042688369751</v>
+        <v>4.334816932678223</v>
       </c>
       <c r="E118" t="n">
-        <v>8.416969299316406</v>
+        <v>7.283968925476074</v>
       </c>
       <c r="F118" t="n">
-        <v>12.58331489562988</v>
+        <v>2.797568321228027</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>12.61268615722656</v>
+        <v>8.815841674804688</v>
       </c>
       <c r="B119" t="n">
-        <v>17.16214561462402</v>
+        <v>4.000357627868652</v>
       </c>
       <c r="C119" t="n">
-        <v>5.466404914855957</v>
+        <v>5.417765617370605</v>
       </c>
       <c r="D119" t="n">
-        <v>12.89947319030762</v>
+        <v>3.696654558181763</v>
       </c>
       <c r="E119" t="n">
-        <v>9.79036808013916</v>
+        <v>9.33893871307373</v>
       </c>
       <c r="F119" t="n">
-        <v>13.91312026977539</v>
+        <v>5.336935043334961</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>11.17227745056152</v>
+        <v>6.024065494537354</v>
       </c>
       <c r="B120" t="n">
-        <v>15.24990367889404</v>
+        <v>1.676270246505737</v>
       </c>
       <c r="C120" t="n">
-        <v>4.83830738067627</v>
+        <v>4.743134498596191</v>
       </c>
       <c r="D120" t="n">
-        <v>12.56532001495361</v>
+        <v>4.027512550354004</v>
       </c>
       <c r="E120" t="n">
-        <v>11.96519756317139</v>
+        <v>11.78239345550537</v>
       </c>
       <c r="F120" t="n">
-        <v>16.10801887512207</v>
+        <v>7.890754699707031</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>9.259573936462402</v>
+        <v>3.648661136627197</v>
       </c>
       <c r="B121" t="n">
-        <v>13.43188285827637</v>
+        <v>-0.7448875308036804</v>
       </c>
       <c r="C121" t="n">
-        <v>4.467642784118652</v>
+        <v>4.522809028625488</v>
       </c>
       <c r="D121" t="n">
-        <v>11.80052852630615</v>
+        <v>2.352341890335083</v>
       </c>
       <c r="E121" t="n">
-        <v>13.88674449920654</v>
+        <v>14.38571453094482</v>
       </c>
       <c r="F121" t="n">
-        <v>18.40633201599121</v>
+        <v>10.63117790222168</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>7.95937967300415</v>
+        <v>0.8861280083656311</v>
       </c>
       <c r="B122" t="n">
-        <v>12.12843894958496</v>
+        <v>-4.356568336486816</v>
       </c>
       <c r="C122" t="n">
-        <v>4.800379753112793</v>
+        <v>4.999947547912598</v>
       </c>
       <c r="D122" t="n">
-        <v>12.02230644226074</v>
+        <v>2.802272081375122</v>
       </c>
       <c r="E122" t="n">
-        <v>15.02665424346924</v>
+        <v>17.83062934875488</v>
       </c>
       <c r="F122" t="n">
-        <v>20.88995361328125</v>
+        <v>13.64640235900879</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6.31920862197876</v>
+        <v>-0.1011194586753845</v>
       </c>
       <c r="B123" t="n">
-        <v>11.06478118896484</v>
+        <v>-6.290959358215332</v>
       </c>
       <c r="C123" t="n">
-        <v>5.554388999938965</v>
+        <v>5.890583992004395</v>
       </c>
       <c r="D123" t="n">
-        <v>12.53136825561523</v>
+        <v>3.599747896194458</v>
       </c>
       <c r="E123" t="n">
-        <v>16.46009635925293</v>
+        <v>20.91813087463379</v>
       </c>
       <c r="F123" t="n">
-        <v>23.73584938049316</v>
+        <v>15.88543128967285</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4.802965641021729</v>
+        <v>-1.2566237449646</v>
       </c>
       <c r="B124" t="n">
-        <v>10.04786682128906</v>
+        <v>-8.343802452087402</v>
       </c>
       <c r="C124" t="n">
-        <v>6.743279457092285</v>
+        <v>6.703438758850098</v>
       </c>
       <c r="D124" t="n">
-        <v>13.03888130187988</v>
+        <v>4.093043327331543</v>
       </c>
       <c r="E124" t="n">
-        <v>16.97161293029785</v>
+        <v>21.84143447875977</v>
       </c>
       <c r="F124" t="n">
-        <v>25.76670265197754</v>
+        <v>17.79897689819336</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3.561832904815674</v>
+        <v>-2.770114421844482</v>
       </c>
       <c r="B125" t="n">
-        <v>9.085644721984863</v>
+        <v>-10.84043788909912</v>
       </c>
       <c r="C125" t="n">
-        <v>7.991209983825684</v>
+        <v>8.326188087463379</v>
       </c>
       <c r="D125" t="n">
-        <v>14.49263858795166</v>
+        <v>5.831143379211426</v>
       </c>
       <c r="E125" t="n">
-        <v>17.26568603515625</v>
+        <v>22.7805118560791</v>
       </c>
       <c r="F125" t="n">
-        <v>28.13548469543457</v>
+        <v>18.0942211151123</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2.987274646759033</v>
+        <v>-3.910285472869873</v>
       </c>
       <c r="B126" t="n">
-        <v>7.438170433044434</v>
+        <v>-12.38433742523193</v>
       </c>
       <c r="C126" t="n">
-        <v>9.049834251403809</v>
+        <v>11.66048526763916</v>
       </c>
       <c r="D126" t="n">
-        <v>15.46405029296875</v>
+        <v>7.30942440032959</v>
       </c>
       <c r="E126" t="n">
-        <v>16.84111404418945</v>
+        <v>22.44972229003906</v>
       </c>
       <c r="F126" t="n">
-        <v>29.90445518493652</v>
+        <v>17.00813293457031</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.487570285797119</v>
+        <v>-4.115357875823975</v>
       </c>
       <c r="B127" t="n">
-        <v>6.475529670715332</v>
+        <v>-12.92031383514404</v>
       </c>
       <c r="C127" t="n">
-        <v>11.23060321807861</v>
+        <v>15.02703762054443</v>
       </c>
       <c r="D127" t="n">
-        <v>17.00569152832031</v>
+        <v>9.652440071105957</v>
       </c>
       <c r="E127" t="n">
-        <v>15.00042819976807</v>
+        <v>17.92409896850586</v>
       </c>
       <c r="F127" t="n">
-        <v>30.88234901428223</v>
+        <v>13.60737228393555</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.6638532280921936</v>
+        <v>-3.337798595428467</v>
       </c>
       <c r="B128" t="n">
-        <v>5.04908275604248</v>
+        <v>-12.6792631149292</v>
       </c>
       <c r="C128" t="n">
-        <v>13.64480590820312</v>
+        <v>19.42657279968262</v>
       </c>
       <c r="D128" t="n">
-        <v>18.93924331665039</v>
+        <v>12.93988990783691</v>
       </c>
       <c r="E128" t="n">
-        <v>9.87825870513916</v>
+        <v>10.55918216705322</v>
       </c>
       <c r="F128" t="n">
-        <v>29.33086204528809</v>
+        <v>7.674574851989746</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.2892709374427795</v>
+        <v>-2.652530193328857</v>
       </c>
       <c r="B129" t="n">
-        <v>4.22274112701416</v>
+        <v>-12.79177761077881</v>
       </c>
       <c r="C129" t="n">
-        <v>16.72466468811035</v>
+        <v>24.82461357116699</v>
       </c>
       <c r="D129" t="n">
-        <v>21.73453521728516</v>
+        <v>17.00019645690918</v>
       </c>
       <c r="E129" t="n">
-        <v>2.80318546295166</v>
+        <v>1.293825149536133</v>
       </c>
       <c r="F129" t="n">
-        <v>25.26494216918945</v>
+        <v>-0.05198485404253006</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.2722077965736389</v>
+        <v>-1.19662618637085</v>
       </c>
       <c r="B130" t="n">
-        <v>4.04253101348877</v>
+        <v>-11.78017330169678</v>
       </c>
       <c r="C130" t="n">
-        <v>20.56465911865234</v>
+        <v>30.32718658447266</v>
       </c>
       <c r="D130" t="n">
-        <v>25.35263442993164</v>
+        <v>22.79810333251953</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.568830490112305</v>
+        <v>-10.8669261932373</v>
       </c>
       <c r="F130" t="n">
-        <v>18.35097694396973</v>
+        <v>-8.655768394470215</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.91396951675415</v>
+        <v>0.4534154534339905</v>
       </c>
       <c r="B131" t="n">
-        <v>3.878103971481323</v>
+        <v>-9.955714225769043</v>
       </c>
       <c r="C131" t="n">
-        <v>25.9184398651123</v>
+        <v>36.72049713134766</v>
       </c>
       <c r="D131" t="n">
-        <v>29.51139450073242</v>
+        <v>27.79168891906738</v>
       </c>
       <c r="E131" t="n">
-        <v>-19.88309478759766</v>
+        <v>-22.22511291503906</v>
       </c>
       <c r="F131" t="n">
-        <v>7.069904327392578</v>
+        <v>-18.14383697509766</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3.430569171905518</v>
+        <v>2.973255634307861</v>
       </c>
       <c r="B132" t="n">
-        <v>5.23441219329834</v>
+        <v>-6.99628734588623</v>
       </c>
       <c r="C132" t="n">
-        <v>32.24539947509766</v>
+        <v>43.29410171508789</v>
       </c>
       <c r="D132" t="n">
-        <v>35.58612060546875</v>
+        <v>34.29996871948242</v>
       </c>
       <c r="E132" t="n">
-        <v>-31.78198623657227</v>
+        <v>-31.70876502990723</v>
       </c>
       <c r="F132" t="n">
-        <v>-5.546109199523926</v>
+        <v>-25.68502235412598</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5.864517688751221</v>
+        <v>6.470871448516846</v>
       </c>
       <c r="B133" t="n">
-        <v>7.913895606994629</v>
+        <v>-4.000090599060059</v>
       </c>
       <c r="C133" t="n">
-        <v>38.20671463012695</v>
+        <v>49.20261383056641</v>
       </c>
       <c r="D133" t="n">
-        <v>42.58428192138672</v>
+        <v>40.50544738769531</v>
       </c>
       <c r="E133" t="n">
-        <v>-40.54299163818359</v>
+        <v>-37.92148590087891</v>
       </c>
       <c r="F133" t="n">
-        <v>-17.99041938781738</v>
+        <v>-32.16725540161133</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>9.407598495483398</v>
+        <v>10.54849147796631</v>
       </c>
       <c r="B134" t="n">
-        <v>10.60482978820801</v>
+        <v>-0.2861377596855164</v>
       </c>
       <c r="C134" t="n">
-        <v>44.60543060302734</v>
+        <v>55.65846633911133</v>
       </c>
       <c r="D134" t="n">
-        <v>49.01313018798828</v>
+        <v>46.96036911010742</v>
       </c>
       <c r="E134" t="n">
-        <v>-43.52858352661133</v>
+        <v>-40.19524002075195</v>
       </c>
       <c r="F134" t="n">
-        <v>-26.98867416381836</v>
+        <v>-33.26572036743164</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>13.32530879974365</v>
+        <v>14.30334186553955</v>
       </c>
       <c r="B135" t="n">
-        <v>14.01436710357666</v>
+        <v>4.300108909606934</v>
       </c>
       <c r="C135" t="n">
-        <v>49.66412734985352</v>
+        <v>61.04327011108398</v>
       </c>
       <c r="D135" t="n">
-        <v>54.67681884765625</v>
+        <v>52.41736602783203</v>
       </c>
       <c r="E135" t="n">
-        <v>-41.01863098144531</v>
+        <v>-38.9050407409668</v>
       </c>
       <c r="F135" t="n">
-        <v>-31.2160758972168</v>
+        <v>-32.3308219909668</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>16.81561660766602</v>
+        <v>17.99888610839844</v>
       </c>
       <c r="B136" t="n">
-        <v>17.8128662109375</v>
+        <v>8.690563201904297</v>
       </c>
       <c r="C136" t="n">
-        <v>53.02542495727539</v>
+        <v>65.55384063720703</v>
       </c>
       <c r="D136" t="n">
-        <v>59.83730316162109</v>
+        <v>57.60918426513672</v>
       </c>
       <c r="E136" t="n">
-        <v>-33.74232864379883</v>
+        <v>-33.08967590332031</v>
       </c>
       <c r="F136" t="n">
-        <v>-30.08967018127441</v>
+        <v>-29.07196235656738</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>20.13756942749023</v>
+        <v>22.92666625976562</v>
       </c>
       <c r="B137" t="n">
-        <v>21.47151947021484</v>
+        <v>12.89675045013428</v>
       </c>
       <c r="C137" t="n">
-        <v>54.10702514648438</v>
+        <v>68.47806549072266</v>
       </c>
       <c r="D137" t="n">
-        <v>62.00178527832031</v>
+        <v>59.01203155517578</v>
       </c>
       <c r="E137" t="n">
-        <v>-23.96813774108887</v>
+        <v>-25.18867492675781</v>
       </c>
       <c r="F137" t="n">
-        <v>-25.01793670654297</v>
+        <v>-24.09909057617188</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>23.53323173522949</v>
+        <v>26.05499649047852</v>
       </c>
       <c r="B138" t="n">
-        <v>24.76387596130371</v>
+        <v>17.42653465270996</v>
       </c>
       <c r="C138" t="n">
-        <v>54.01570510864258</v>
+        <v>67.87445831298828</v>
       </c>
       <c r="D138" t="n">
-        <v>63.3194580078125</v>
+        <v>61.54499053955078</v>
       </c>
       <c r="E138" t="n">
-        <v>-14.46730804443359</v>
+        <v>-17.30570220947266</v>
       </c>
       <c r="F138" t="n">
-        <v>-17.33541488647461</v>
+        <v>-17.46427726745605</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>26.00849723815918</v>
+        <v>29.5886173248291</v>
       </c>
       <c r="B139" t="n">
-        <v>28.17247772216797</v>
+        <v>21.48470497131348</v>
       </c>
       <c r="C139" t="n">
-        <v>50.40753936767578</v>
+        <v>66.91218566894531</v>
       </c>
       <c r="D139" t="n">
-        <v>60.96384811401367</v>
+        <v>60.66816711425781</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.057201862335205</v>
+        <v>-10.25733184814453</v>
       </c>
       <c r="F139" t="n">
-        <v>-9.829790115356445</v>
+        <v>-10.670578956604</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>28.2206916809082</v>
+        <v>32.14756393432617</v>
       </c>
       <c r="B140" t="n">
-        <v>30.89780044555664</v>
+        <v>24.69942855834961</v>
       </c>
       <c r="C140" t="n">
-        <v>46.7397575378418</v>
+        <v>63.39299011230469</v>
       </c>
       <c r="D140" t="n">
-        <v>58.35998916625977</v>
+        <v>58.03363418579102</v>
       </c>
       <c r="E140" t="n">
-        <v>-1.937476634979248</v>
+        <v>-4.735198020935059</v>
       </c>
       <c r="F140" t="n">
-        <v>-2.733156681060791</v>
+        <v>-6.981189727783203</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>30.31411361694336</v>
+        <v>34.22246551513672</v>
       </c>
       <c r="B141" t="n">
-        <v>33.08274459838867</v>
+        <v>27.29484558105469</v>
       </c>
       <c r="C141" t="n">
-        <v>40.13079071044922</v>
+        <v>57.6546745300293</v>
       </c>
       <c r="D141" t="n">
-        <v>53.71134948730469</v>
+        <v>54.28509521484375</v>
       </c>
       <c r="E141" t="n">
-        <v>1.194984436035156</v>
+        <v>-2.657509803771973</v>
       </c>
       <c r="F141" t="n">
-        <v>2.464303970336914</v>
+        <v>-3.974953174591064</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>31.76618385314941</v>
+        <v>35.44582748413086</v>
       </c>
       <c r="B142" t="n">
-        <v>35.97172546386719</v>
+        <v>28.99286460876465</v>
       </c>
       <c r="C142" t="n">
-        <v>33.92512893676758</v>
+        <v>50.71768569946289</v>
       </c>
       <c r="D142" t="n">
-        <v>48.53556060791016</v>
+        <v>47.58101654052734</v>
       </c>
       <c r="E142" t="n">
-        <v>2.328441619873047</v>
+        <v>-1.782870769500732</v>
       </c>
       <c r="F142" t="n">
-        <v>6.19603157043457</v>
+        <v>-2.277777671813965</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>32.88447570800781</v>
+        <v>36.23454284667969</v>
       </c>
       <c r="B143" t="n">
-        <v>37.32049942016602</v>
+        <v>30.55094337463379</v>
       </c>
       <c r="C143" t="n">
-        <v>27.3643913269043</v>
+        <v>42.44448471069336</v>
       </c>
       <c r="D143" t="n">
-        <v>41.79814147949219</v>
+        <v>40.43159866333008</v>
       </c>
       <c r="E143" t="n">
-        <v>2.471068382263184</v>
+        <v>-3.248795986175537</v>
       </c>
       <c r="F143" t="n">
-        <v>7.304019927978516</v>
+        <v>-2.63770055770874</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>33.75889587402344</v>
+        <v>36.20428466796875</v>
       </c>
       <c r="B144" t="n">
-        <v>38.57216644287109</v>
+        <v>31.73715400695801</v>
       </c>
       <c r="C144" t="n">
-        <v>20.05926513671875</v>
+        <v>34.10746383666992</v>
       </c>
       <c r="D144" t="n">
-        <v>33.98785018920898</v>
+        <v>31.63577842712402</v>
       </c>
       <c r="E144" t="n">
-        <v>1.594985008239746</v>
+        <v>-4.27304744720459</v>
       </c>
       <c r="F144" t="n">
-        <v>7.445345878601074</v>
+        <v>-3.903391599655151</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>34.26133346557617</v>
+        <v>37.02706909179688</v>
       </c>
       <c r="B145" t="n">
-        <v>39.21776962280273</v>
+        <v>31.95977020263672</v>
       </c>
       <c r="C145" t="n">
-        <v>12.63702392578125</v>
+        <v>26.2064037322998</v>
       </c>
       <c r="D145" t="n">
-        <v>26.73995208740234</v>
+        <v>24.41827201843262</v>
       </c>
       <c r="E145" t="n">
-        <v>0.6720428466796875</v>
+        <v>-7.266583919525146</v>
       </c>
       <c r="F145" t="n">
-        <v>5.733908653259277</v>
+        <v>-6.728583335876465</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>35.30496978759766</v>
+        <v>36.81016540527344</v>
       </c>
       <c r="B146" t="n">
-        <v>39.72545623779297</v>
+        <v>32.27976226806641</v>
       </c>
       <c r="C146" t="n">
-        <v>5.689848899841309</v>
+        <v>18.05717468261719</v>
       </c>
       <c r="D146" t="n">
-        <v>18.98322105407715</v>
+        <v>16.70573806762695</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.6459178924560547</v>
+        <v>-9.434447288513184</v>
       </c>
       <c r="F146" t="n">
-        <v>3.951912879943848</v>
+        <v>-8.765737533569336</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>35.28768157958984</v>
+        <v>36.35408020019531</v>
       </c>
       <c r="B147" t="n">
-        <v>39.73944473266602</v>
+        <v>32.14517974853516</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1235626339912415</v>
+        <v>12.04126739501953</v>
       </c>
       <c r="D147" t="n">
-        <v>11.61956596374512</v>
+        <v>9.89747142791748</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.7839560508728027</v>
+        <v>-10.58584308624268</v>
       </c>
       <c r="F147" t="n">
-        <v>2.443949699401855</v>
+        <v>-10.34949111938477</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>35.9718132019043</v>
+        <v>36.57391357421875</v>
       </c>
       <c r="B148" t="n">
-        <v>39.67966461181641</v>
+        <v>32.0962028503418</v>
       </c>
       <c r="C148" t="n">
-        <v>-4.171622276306152</v>
+        <v>7.82681941986084</v>
       </c>
       <c r="D148" t="n">
-        <v>4.898869514465332</v>
+        <v>4.787487983703613</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.172397613525391</v>
+        <v>-12.48688983917236</v>
       </c>
       <c r="F148" t="n">
-        <v>1.167364954948425</v>
+        <v>-12.88704681396484</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>36.39017486572266</v>
+        <v>36.41680526733398</v>
       </c>
       <c r="B149" t="n">
-        <v>39.49742126464844</v>
+        <v>32.63991928100586</v>
       </c>
       <c r="C149" t="n">
-        <v>-6.467886924743652</v>
+        <v>5.622565269470215</v>
       </c>
       <c r="D149" t="n">
-        <v>1.408795475959778</v>
+        <v>1.240397572517395</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.570465087890625</v>
+        <v>-13.1224422454834</v>
       </c>
       <c r="F149" t="n">
-        <v>0.9732345938682556</v>
+        <v>-14.03171062469482</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>37.15765380859375</v>
+        <v>36.8440055847168</v>
       </c>
       <c r="B150" t="n">
-        <v>39.32718276977539</v>
+        <v>32.78140640258789</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.525698661804199</v>
+        <v>4.731640815734863</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.026692271232605</v>
+        <v>0.4500857591629028</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.603988647460938</v>
+        <v>-13.76726055145264</v>
       </c>
       <c r="F150" t="n">
-        <v>0.7930130362510681</v>
+        <v>-15.47550678253174</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>37.35542297363281</v>
+        <v>38.84518051147461</v>
       </c>
       <c r="B151" t="n">
-        <v>39.18062973022461</v>
+        <v>33.58462142944336</v>
       </c>
       <c r="C151" t="n">
-        <v>-6.585667610168457</v>
+        <v>4.755555152893066</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.173302531242371</v>
+        <v>0.07318222522735596</v>
       </c>
       <c r="E151" t="n">
-        <v>-3.341675281524658</v>
+        <v>-14.41175842285156</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.4870825409889221</v>
+        <v>-16.20422554016113</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>38.05731964111328</v>
+        <v>40.78763198852539</v>
       </c>
       <c r="B152" t="n">
-        <v>39.16582489013672</v>
+        <v>35.36297607421875</v>
       </c>
       <c r="C152" t="n">
-        <v>-4.341134071350098</v>
+        <v>6.790024757385254</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2428635358810425</v>
+        <v>1.268963932991028</v>
       </c>
       <c r="E152" t="n">
-        <v>-5.37291955947876</v>
+        <v>-15.34188842773438</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.888682007789612</v>
+        <v>-16.44966316223145</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>38.06066131591797</v>
+        <v>41.67521667480469</v>
       </c>
       <c r="B153" t="n">
-        <v>40.46109008789062</v>
+        <v>37.01031112670898</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.918950200080872</v>
+        <v>9.090677261352539</v>
       </c>
       <c r="D153" t="n">
-        <v>2.035043001174927</v>
+        <v>4.968104362487793</v>
       </c>
       <c r="E153" t="n">
-        <v>-7.414067268371582</v>
+        <v>-16.00958824157715</v>
       </c>
       <c r="F153" t="n">
-        <v>-3.995336294174194</v>
+        <v>-18.5695915222168</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>38.43004608154297</v>
+        <v>42.9468879699707</v>
       </c>
       <c r="B154" t="n">
-        <v>40.71736145019531</v>
+        <v>38.94122314453125</v>
       </c>
       <c r="C154" t="n">
-        <v>0.8589351773262024</v>
+        <v>11.86382293701172</v>
       </c>
       <c r="D154" t="n">
-        <v>3.977969408035278</v>
+        <v>7.932759284973145</v>
       </c>
       <c r="E154" t="n">
-        <v>-9.568327903747559</v>
+        <v>-18.17763137817383</v>
       </c>
       <c r="F154" t="n">
-        <v>-7.105108261108398</v>
+        <v>-19.38474082946777</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>38.31682968139648</v>
+        <v>43.86614227294922</v>
       </c>
       <c r="B155" t="n">
-        <v>41.08672332763672</v>
+        <v>39.87516403198242</v>
       </c>
       <c r="C155" t="n">
-        <v>2.707150220870972</v>
+        <v>15.18836784362793</v>
       </c>
       <c r="D155" t="n">
-        <v>6.422661781311035</v>
+        <v>11.68959903717041</v>
       </c>
       <c r="E155" t="n">
-        <v>-12.58256912231445</v>
+        <v>-18.30479621887207</v>
       </c>
       <c r="F155" t="n">
-        <v>-10.50106906890869</v>
+        <v>-21.29479026794434</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>37.98612976074219</v>
+        <v>43.24729919433594</v>
       </c>
       <c r="B156" t="n">
-        <v>41.60843276977539</v>
+        <v>40.48334884643555</v>
       </c>
       <c r="C156" t="n">
-        <v>4.810839653015137</v>
+        <v>18.52944183349609</v>
       </c>
       <c r="D156" t="n">
-        <v>9.023373603820801</v>
+        <v>14.79644966125488</v>
       </c>
       <c r="E156" t="n">
-        <v>-14.63552379608154</v>
+        <v>-19.53020668029785</v>
       </c>
       <c r="F156" t="n">
-        <v>-13.67868137359619</v>
+        <v>-22.44071388244629</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>37.08829116821289</v>
+        <v>42.96939086914062</v>
       </c>
       <c r="B157" t="n">
-        <v>41.78089141845703</v>
+        <v>39.93181610107422</v>
       </c>
       <c r="C157" t="n">
-        <v>7.068757057189941</v>
+        <v>21.71775054931641</v>
       </c>
       <c r="D157" t="n">
-        <v>11.91900253295898</v>
+        <v>17.13863563537598</v>
       </c>
       <c r="E157" t="n">
-        <v>-15.88186931610107</v>
+        <v>-19.1517505645752</v>
       </c>
       <c r="F157" t="n">
-        <v>-14.97935199737549</v>
+        <v>-23.42254829406738</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>35.8389778137207</v>
+        <v>42.20298385620117</v>
       </c>
       <c r="B158" t="n">
-        <v>41.08113098144531</v>
+        <v>38.75869750976562</v>
       </c>
       <c r="C158" t="n">
-        <v>8.531739234924316</v>
+        <v>23.60464286804199</v>
       </c>
       <c r="D158" t="n">
-        <v>14.65953350067139</v>
+        <v>19.18424797058105</v>
       </c>
       <c r="E158" t="n">
-        <v>-15.60851383209229</v>
+        <v>-16.92536354064941</v>
       </c>
       <c r="F158" t="n">
-        <v>-14.87072563171387</v>
+        <v>-23.11048126220703</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>34.64878845214844</v>
+        <v>39.8828125</v>
       </c>
       <c r="B159" t="n">
-        <v>40.08373641967773</v>
+        <v>36.33194351196289</v>
       </c>
       <c r="C159" t="n">
-        <v>9.856381416320801</v>
+        <v>25.05488395690918</v>
       </c>
       <c r="D159" t="n">
-        <v>17.37347984313965</v>
+        <v>19.75436401367188</v>
       </c>
       <c r="E159" t="n">
-        <v>-15.40816020965576</v>
+        <v>-14.78296375274658</v>
       </c>
       <c r="F159" t="n">
-        <v>-13.85357093811035</v>
+        <v>-21.26208686828613</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>32.79843902587891</v>
+        <v>38.12798690795898</v>
       </c>
       <c r="B160" t="n">
-        <v>39.30973815917969</v>
+        <v>34.96858596801758</v>
       </c>
       <c r="C160" t="n">
-        <v>10.87001323699951</v>
+        <v>25.04904747009277</v>
       </c>
       <c r="D160" t="n">
-        <v>19.35056304931641</v>
+        <v>19.7278003692627</v>
       </c>
       <c r="E160" t="n">
-        <v>-11.75496578216553</v>
+        <v>-11.10604381561279</v>
       </c>
       <c r="F160" t="n">
-        <v>-10.26800060272217</v>
+        <v>-18.1252613067627</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>31.10458755493164</v>
+        <v>35.62606811523438</v>
       </c>
       <c r="B161" t="n">
-        <v>37.81338119506836</v>
+        <v>32.51412582397461</v>
       </c>
       <c r="C161" t="n">
-        <v>11.39313888549805</v>
+        <v>23.87285995483398</v>
       </c>
       <c r="D161" t="n">
-        <v>20.44736862182617</v>
+        <v>19.59061241149902</v>
       </c>
       <c r="E161" t="n">
-        <v>-8.109955787658691</v>
+        <v>-6.910963535308838</v>
       </c>
       <c r="F161" t="n">
-        <v>-6.258354663848877</v>
+        <v>-14.20364570617676</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>29.38551902770996</v>
+        <v>33.08911895751953</v>
       </c>
       <c r="B162" t="n">
-        <v>35.48080444335938</v>
+        <v>29.16564750671387</v>
       </c>
       <c r="C162" t="n">
-        <v>11.59175109863281</v>
+        <v>22.58837127685547</v>
       </c>
       <c r="D162" t="n">
-        <v>21.09395599365234</v>
+        <v>17.5342903137207</v>
       </c>
       <c r="E162" t="n">
-        <v>-5.186172485351562</v>
+        <v>-3.449883699417114</v>
       </c>
       <c r="F162" t="n">
-        <v>-1.980200409889221</v>
+        <v>-12.19717407226562</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>27.49267768859863</v>
+        <v>30.48255920410156</v>
       </c>
       <c r="B163" t="n">
-        <v>33.62327575683594</v>
+        <v>25.46523666381836</v>
       </c>
       <c r="C163" t="n">
-        <v>11.17319202423096</v>
+        <v>20.54792022705078</v>
       </c>
       <c r="D163" t="n">
-        <v>20.61480903625488</v>
+        <v>15.64565467834473</v>
       </c>
       <c r="E163" t="n">
-        <v>-2.470053195953369</v>
+        <v>-1.043282032012939</v>
       </c>
       <c r="F163" t="n">
-        <v>1.103405833244324</v>
+        <v>-9.081290245056152</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>24.9278736114502</v>
+        <v>27.27159118652344</v>
       </c>
       <c r="B164" t="n">
-        <v>31.46803665161133</v>
+        <v>22.3924388885498</v>
       </c>
       <c r="C164" t="n">
-        <v>10.71487140655518</v>
+        <v>17.87545394897461</v>
       </c>
       <c r="D164" t="n">
-        <v>19.89733695983887</v>
+        <v>13.21243381500244</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.3725314140319824</v>
+        <v>1.143263816833496</v>
       </c>
       <c r="F164" t="n">
-        <v>3.754530906677246</v>
+        <v>-7.096708297729492</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>22.91636848449707</v>
+        <v>23.653076171875</v>
       </c>
       <c r="B165" t="n">
-        <v>28.7008228302002</v>
+        <v>19.7097282409668</v>
       </c>
       <c r="C165" t="n">
-        <v>9.773944854736328</v>
+        <v>15.57135772705078</v>
       </c>
       <c r="D165" t="n">
-        <v>18.68446922302246</v>
+        <v>10.69397926330566</v>
       </c>
       <c r="E165" t="n">
-        <v>1.54782772064209</v>
+        <v>2.25621509552002</v>
       </c>
       <c r="F165" t="n">
-        <v>5.458852767944336</v>
+        <v>-5.937560081481934</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>20.62395286560059</v>
+        <v>20.66202926635742</v>
       </c>
       <c r="B166" t="n">
-        <v>26.56910705566406</v>
+        <v>15.83425903320312</v>
       </c>
       <c r="C166" t="n">
-        <v>8.688429832458496</v>
+        <v>12.36659240722656</v>
       </c>
       <c r="D166" t="n">
-        <v>17.49213600158691</v>
+        <v>8.830859184265137</v>
       </c>
       <c r="E166" t="n">
-        <v>2.989198684692383</v>
+        <v>3.508183479309082</v>
       </c>
       <c r="F166" t="n">
-        <v>7.863930702209473</v>
+        <v>-4.338031768798828</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>18.70052528381348</v>
+        <v>17.79060745239258</v>
       </c>
       <c r="B167" t="n">
-        <v>24.1517505645752</v>
+        <v>13.07168006896973</v>
       </c>
       <c r="C167" t="n">
-        <v>7.79747486114502</v>
+        <v>10.19278240203857</v>
       </c>
       <c r="D167" t="n">
-        <v>16.81696891784668</v>
+        <v>6.408495903015137</v>
       </c>
       <c r="E167" t="n">
-        <v>4.870852470397949</v>
+        <v>4.739806175231934</v>
       </c>
       <c r="F167" t="n">
-        <v>9.355093955993652</v>
+        <v>-2.75297999382019</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>16.37315368652344</v>
+        <v>14.59169387817383</v>
       </c>
       <c r="B168" t="n">
-        <v>21.58060264587402</v>
+        <v>9.790329933166504</v>
       </c>
       <c r="C168" t="n">
-        <v>6.888894081115723</v>
+        <v>8.877995491027832</v>
       </c>
       <c r="D168" t="n">
-        <v>15.20709419250488</v>
+        <v>5.314269065856934</v>
       </c>
       <c r="E168" t="n">
-        <v>6.551874160766602</v>
+        <v>5.571412086486816</v>
       </c>
       <c r="F168" t="n">
-        <v>10.83036613464355</v>
+        <v>-0.7230802178382874</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>14.76905250549316</v>
+        <v>11.65175819396973</v>
       </c>
       <c r="B169" t="n">
-        <v>19.49133491516113</v>
+        <v>6.847043037414551</v>
       </c>
       <c r="C169" t="n">
-        <v>6.169381141662598</v>
+        <v>6.275965690612793</v>
       </c>
       <c r="D169" t="n">
-        <v>14.29983711242676</v>
+        <v>4.297123908996582</v>
       </c>
       <c r="E169" t="n">
-        <v>8.368096351623535</v>
+        <v>7.33852481842041</v>
       </c>
       <c r="F169" t="n">
-        <v>12.62884712219238</v>
+        <v>2.868318557739258</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>12.55225086212158</v>
+        <v>8.931612014770508</v>
       </c>
       <c r="B170" t="n">
-        <v>17.11425399780273</v>
+        <v>3.99181056022644</v>
       </c>
       <c r="C170" t="n">
-        <v>5.407036781311035</v>
+        <v>5.35604190826416</v>
       </c>
       <c r="D170" t="n">
-        <v>12.87198638916016</v>
+        <v>3.640885591506958</v>
       </c>
       <c r="E170" t="n">
-        <v>9.707272529602051</v>
+        <v>9.371781349182129</v>
       </c>
       <c r="F170" t="n">
-        <v>13.95535659790039</v>
+        <v>5.487368583679199</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>11.09819412231445</v>
+        <v>6.119766712188721</v>
       </c>
       <c r="B171" t="n">
-        <v>15.19888877868652</v>
+        <v>1.622206449508667</v>
       </c>
       <c r="C171" t="n">
-        <v>4.754454612731934</v>
+        <v>4.690791130065918</v>
       </c>
       <c r="D171" t="n">
-        <v>12.52835464477539</v>
+        <v>3.943362474441528</v>
       </c>
       <c r="E171" t="n">
-        <v>11.85614109039307</v>
+        <v>11.87249088287354</v>
       </c>
       <c r="F171" t="n">
-        <v>16.14183235168457</v>
+        <v>8.134819984436035</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>9.20811939239502</v>
+        <v>3.719261646270752</v>
       </c>
       <c r="B172" t="n">
-        <v>13.37358474731445</v>
+        <v>-0.866646945476532</v>
       </c>
       <c r="C172" t="n">
-        <v>4.36815357208252</v>
+        <v>4.464190483093262</v>
       </c>
       <c r="D172" t="n">
-        <v>11.77450561523438</v>
+        <v>2.263222932815552</v>
       </c>
       <c r="E172" t="n">
-        <v>13.78461933135986</v>
+        <v>14.59222316741943</v>
       </c>
       <c r="F172" t="n">
-        <v>18.44671630859375</v>
+        <v>10.85517692565918</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>7.88944673538208</v>
+        <v>0.9721646904945374</v>
       </c>
       <c r="B173" t="n">
-        <v>12.0691967010498</v>
+        <v>-4.453125953674316</v>
       </c>
       <c r="C173" t="n">
-        <v>4.734519004821777</v>
+        <v>4.98593807220459</v>
       </c>
       <c r="D173" t="n">
-        <v>12.00101947784424</v>
+        <v>2.630975008010864</v>
       </c>
       <c r="E173" t="n">
-        <v>14.94883060455322</v>
+        <v>18.07710075378418</v>
       </c>
       <c r="F173" t="n">
-        <v>20.91860008239746</v>
+        <v>13.91857528686523</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>6.231712818145752</v>
+        <v>-0.09622901678085327</v>
       </c>
       <c r="B174" t="n">
-        <v>10.98899173736572</v>
+        <v>-6.450640678405762</v>
       </c>
       <c r="C174" t="n">
-        <v>5.444561958312988</v>
+        <v>5.863987922668457</v>
       </c>
       <c r="D174" t="n">
-        <v>12.46716785430908</v>
+        <v>3.438983201980591</v>
       </c>
       <c r="E174" t="n">
-        <v>16.37858581542969</v>
+        <v>21.14007949829102</v>
       </c>
       <c r="F174" t="n">
-        <v>23.73505592346191</v>
+        <v>16.12708854675293</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>4.775635242462158</v>
+        <v>-1.249734401702881</v>
       </c>
       <c r="B175" t="n">
-        <v>9.943824768066406</v>
+        <v>-8.569216728210449</v>
       </c>
       <c r="C175" t="n">
-        <v>6.674258232116699</v>
+        <v>6.724270820617676</v>
       </c>
       <c r="D175" t="n">
-        <v>13.00151252746582</v>
+        <v>3.902871370315552</v>
       </c>
       <c r="E175" t="n">
-        <v>16.8716869354248</v>
+        <v>22.20008087158203</v>
       </c>
       <c r="F175" t="n">
-        <v>25.75364875793457</v>
+        <v>18.06913757324219</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>3.518560886383057</v>
+        <v>-2.788819789886475</v>
       </c>
       <c r="B176" t="n">
-        <v>8.99006462097168</v>
+        <v>-11.02727031707764</v>
       </c>
       <c r="C176" t="n">
-        <v>7.927128791809082</v>
+        <v>8.385680198669434</v>
       </c>
       <c r="D176" t="n">
-        <v>14.42903900146484</v>
+        <v>5.595536231994629</v>
       </c>
       <c r="E176" t="n">
-        <v>17.19880294799805</v>
+        <v>23.18899154663086</v>
       </c>
       <c r="F176" t="n">
-        <v>28.10357093811035</v>
+        <v>18.39203643798828</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2.930538654327393</v>
+        <v>-3.874637126922607</v>
       </c>
       <c r="B177" t="n">
-        <v>7.329930305480957</v>
+        <v>-12.55195140838623</v>
       </c>
       <c r="C177" t="n">
-        <v>9.006829261779785</v>
+        <v>11.73551654815674</v>
       </c>
       <c r="D177" t="n">
-        <v>15.40689945220947</v>
+        <v>7.127995491027832</v>
       </c>
       <c r="E177" t="n">
-        <v>16.73714828491211</v>
+        <v>22.80742263793945</v>
       </c>
       <c r="F177" t="n">
-        <v>29.85885047912598</v>
+        <v>17.2440013885498</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1.453543186187744</v>
+        <v>-4.093684673309326</v>
       </c>
       <c r="B178" t="n">
-        <v>6.405701637268066</v>
+        <v>-13.12887859344482</v>
       </c>
       <c r="C178" t="n">
-        <v>11.18970775604248</v>
+        <v>15.15612602233887</v>
       </c>
       <c r="D178" t="n">
-        <v>16.93441390991211</v>
+        <v>9.446578025817871</v>
       </c>
       <c r="E178" t="n">
-        <v>14.89915180206299</v>
+        <v>18.25412368774414</v>
       </c>
       <c r="F178" t="n">
-        <v>30.82987403869629</v>
+        <v>13.81205940246582</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.6229329705238342</v>
+        <v>-3.301167964935303</v>
       </c>
       <c r="B179" t="n">
-        <v>4.973912239074707</v>
+        <v>-12.93876934051514</v>
       </c>
       <c r="C179" t="n">
-        <v>13.60029888153076</v>
+        <v>19.61240577697754</v>
       </c>
       <c r="D179" t="n">
-        <v>18.88636016845703</v>
+        <v>12.70999431610107</v>
       </c>
       <c r="E179" t="n">
-        <v>9.779507637023926</v>
+        <v>10.8107213973999</v>
       </c>
       <c r="F179" t="n">
-        <v>29.26341819763184</v>
+        <v>7.828064918518066</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.2635236382484436</v>
+        <v>-2.632972240447998</v>
       </c>
       <c r="B180" t="n">
-        <v>4.143500328063965</v>
+        <v>-12.88214015960693</v>
       </c>
       <c r="C180" t="n">
-        <v>16.72013664245605</v>
+        <v>24.98748779296875</v>
       </c>
       <c r="D180" t="n">
-        <v>21.69722175598145</v>
+        <v>16.84612083435059</v>
       </c>
       <c r="E180" t="n">
-        <v>2.709692001342773</v>
+        <v>1.527843475341797</v>
       </c>
       <c r="F180" t="n">
-        <v>25.20336151123047</v>
+        <v>-0.02815825305879116</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.2668519616127014</v>
+        <v>-1.173932552337646</v>
       </c>
       <c r="B181" t="n">
-        <v>3.942084074020386</v>
+        <v>-11.96680736541748</v>
       </c>
       <c r="C181" t="n">
-        <v>20.57884979248047</v>
+        <v>30.49964332580566</v>
       </c>
       <c r="D181" t="n">
-        <v>25.33382034301758</v>
+        <v>22.64273834228516</v>
       </c>
       <c r="E181" t="n">
-        <v>-7.7113037109375</v>
+        <v>-10.57671546936035</v>
       </c>
       <c r="F181" t="n">
-        <v>18.30373573303223</v>
+        <v>-8.763503074645996</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1.858004093170166</v>
+        <v>0.4766870141029358</v>
       </c>
       <c r="B182" t="n">
-        <v>3.825169324874878</v>
+        <v>-10.10743236541748</v>
       </c>
       <c r="C182" t="n">
-        <v>25.94822692871094</v>
+        <v>36.95430374145508</v>
       </c>
       <c r="D182" t="n">
-        <v>29.47723388671875</v>
+        <v>27.73560905456543</v>
       </c>
       <c r="E182" t="n">
-        <v>-20.04755401611328</v>
+        <v>-21.95962715148926</v>
       </c>
       <c r="F182" t="n">
-        <v>7.010305404663086</v>
+        <v>-18.32950973510742</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>3.412813663482666</v>
+        <v>3.134632587432861</v>
       </c>
       <c r="B183" t="n">
-        <v>5.176798820495605</v>
+        <v>-7.14633846282959</v>
       </c>
       <c r="C183" t="n">
-        <v>32.30869674682617</v>
+        <v>43.49021530151367</v>
       </c>
       <c r="D183" t="n">
-        <v>35.58048629760742</v>
+        <v>34.33003234863281</v>
       </c>
       <c r="E183" t="n">
-        <v>-31.94031143188477</v>
+        <v>-31.37130737304688</v>
       </c>
       <c r="F183" t="n">
-        <v>-5.639084339141846</v>
+        <v>-25.94772911071777</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>5.881474018096924</v>
+        <v>6.595844745635986</v>
       </c>
       <c r="B184" t="n">
-        <v>7.853062629699707</v>
+        <v>-4.06775951385498</v>
       </c>
       <c r="C184" t="n">
-        <v>38.27362442016602</v>
+        <v>49.5501708984375</v>
       </c>
       <c r="D184" t="n">
-        <v>42.57884979248047</v>
+        <v>40.56593704223633</v>
       </c>
       <c r="E184" t="n">
-        <v>-40.64839172363281</v>
+        <v>-37.41671371459961</v>
       </c>
       <c r="F184" t="n">
-        <v>-18.08620452880859</v>
+        <v>-32.40466690063477</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>9.435481071472168</v>
+        <v>10.61547088623047</v>
       </c>
       <c r="B185" t="n">
-        <v>10.54028129577637</v>
+        <v>-0.3359290957450867</v>
       </c>
       <c r="C185" t="n">
-        <v>44.71681213378906</v>
+        <v>55.95883941650391</v>
       </c>
       <c r="D185" t="n">
-        <v>49.03749465942383</v>
+        <v>47.03353118896484</v>
       </c>
       <c r="E185" t="n">
-        <v>-43.57588577270508</v>
+        <v>-39.58154678344727</v>
       </c>
       <c r="F185" t="n">
-        <v>-27.06426811218262</v>
+        <v>-33.43970108032227</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>13.34465408325195</v>
+        <v>14.44140148162842</v>
       </c>
       <c r="B186" t="n">
-        <v>13.98366832733154</v>
+        <v>4.277544975280762</v>
       </c>
       <c r="C186" t="n">
-        <v>49.76112365722656</v>
+        <v>61.30720901489258</v>
       </c>
       <c r="D186" t="n">
-        <v>54.68487548828125</v>
+        <v>52.52753829956055</v>
       </c>
       <c r="E186" t="n">
-        <v>-41.01515579223633</v>
+        <v>-38.09379196166992</v>
       </c>
       <c r="F186" t="n">
-        <v>-31.31060600280762</v>
+        <v>-32.35427856445312</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>16.86109352111816</v>
+        <v>18.12207794189453</v>
       </c>
       <c r="B187" t="n">
-        <v>17.74593925476074</v>
+        <v>8.728870391845703</v>
       </c>
       <c r="C187" t="n">
-        <v>53.10050964355469</v>
+        <v>65.79684448242188</v>
       </c>
       <c r="D187" t="n">
-        <v>59.84103012084961</v>
+        <v>57.75270462036133</v>
       </c>
       <c r="E187" t="n">
-        <v>-33.69398880004883</v>
+        <v>-32.18704223632812</v>
       </c>
       <c r="F187" t="n">
-        <v>-30.17086410522461</v>
+        <v>-28.92392921447754</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>20.16943740844727</v>
+        <v>22.99433135986328</v>
       </c>
       <c r="B188" t="n">
-        <v>21.45020294189453</v>
+        <v>12.98864650726318</v>
       </c>
       <c r="C188" t="n">
-        <v>54.17689514160156</v>
+        <v>68.60417175292969</v>
       </c>
       <c r="D188" t="n">
-        <v>61.99237823486328</v>
+        <v>59.16304016113281</v>
       </c>
       <c r="E188" t="n">
-        <v>-23.91395950317383</v>
+        <v>-24.18178749084473</v>
       </c>
       <c r="F188" t="n">
-        <v>-25.03715133666992</v>
+        <v>-23.84101104736328</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>23.5556697845459</v>
+        <v>26.11988258361816</v>
       </c>
       <c r="B189" t="n">
-        <v>24.73408699035645</v>
+        <v>17.52238655090332</v>
       </c>
       <c r="C189" t="n">
-        <v>54.03877639770508</v>
+        <v>67.92477416992188</v>
       </c>
       <c r="D189" t="n">
-        <v>63.32901382446289</v>
+        <v>61.65145111083984</v>
       </c>
       <c r="E189" t="n">
-        <v>-14.43965530395508</v>
+        <v>-16.36789703369141</v>
       </c>
       <c r="F189" t="n">
-        <v>-17.37644958496094</v>
+        <v>-17.04645538330078</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>26.02297401428223</v>
+        <v>29.60760116577148</v>
       </c>
       <c r="B190" t="n">
-        <v>28.13092422485352</v>
+        <v>21.56679534912109</v>
       </c>
       <c r="C190" t="n">
-        <v>50.40528869628906</v>
+        <v>66.96936798095703</v>
       </c>
       <c r="D190" t="n">
-        <v>60.97658538818359</v>
+        <v>60.73022842407227</v>
       </c>
       <c r="E190" t="n">
-        <v>-7.047838687896729</v>
+        <v>-9.43166446685791</v>
       </c>
       <c r="F190" t="n">
-        <v>-9.88836669921875</v>
+        <v>-10.34523010253906</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>28.23832511901855</v>
+        <v>32.13798141479492</v>
       </c>
       <c r="B191" t="n">
-        <v>30.86780548095703</v>
+        <v>24.84596252441406</v>
       </c>
       <c r="C191" t="n">
-        <v>46.67052459716797</v>
+        <v>63.16763687133789</v>
       </c>
       <c r="D191" t="n">
-        <v>58.35604858398438</v>
+        <v>58.12001037597656</v>
       </c>
       <c r="E191" t="n">
-        <v>-1.982668876647949</v>
+        <v>-4.019895076751709</v>
       </c>
       <c r="F191" t="n">
-        <v>-2.796322584152222</v>
+        <v>-6.543806076049805</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>30.3077564239502</v>
+        <v>34.16184616088867</v>
       </c>
       <c r="B192" t="n">
-        <v>33.04919815063477</v>
+        <v>27.44966125488281</v>
       </c>
       <c r="C192" t="n">
-        <v>40.0340576171875</v>
+        <v>57.427001953125</v>
       </c>
       <c r="D192" t="n">
-        <v>53.69741058349609</v>
+        <v>54.30117416381836</v>
       </c>
       <c r="E192" t="n">
-        <v>1.108475685119629</v>
+        <v>-2.166073799133301</v>
       </c>
       <c r="F192" t="n">
-        <v>2.390923500061035</v>
+        <v>-3.579771518707275</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>31.73157119750977</v>
+        <v>35.46547317504883</v>
       </c>
       <c r="B193" t="n">
-        <v>35.9259033203125</v>
+        <v>29.17480659484863</v>
       </c>
       <c r="C193" t="n">
-        <v>33.86015319824219</v>
+        <v>50.28933334350586</v>
       </c>
       <c r="D193" t="n">
-        <v>48.46535491943359</v>
+        <v>47.59878921508789</v>
       </c>
       <c r="E193" t="n">
-        <v>2.225369453430176</v>
+        <v>-1.444670677185059</v>
       </c>
       <c r="F193" t="n">
-        <v>6.152398109436035</v>
+        <v>-1.943514466285706</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>32.83889770507812</v>
+        <v>36.16010665893555</v>
       </c>
       <c r="B194" t="n">
-        <v>37.28165817260742</v>
+        <v>30.74069023132324</v>
       </c>
       <c r="C194" t="n">
-        <v>27.2544002532959</v>
+        <v>42.05544281005859</v>
       </c>
       <c r="D194" t="n">
-        <v>41.7096061706543</v>
+        <v>40.39265823364258</v>
       </c>
       <c r="E194" t="n">
-        <v>2.338698387145996</v>
+        <v>-3.107954978942871</v>
       </c>
       <c r="F194" t="n">
-        <v>7.223763465881348</v>
+        <v>-2.375854969024658</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>33.70666122436523</v>
+        <v>36.16434097290039</v>
       </c>
       <c r="B195" t="n">
-        <v>38.53907775878906</v>
+        <v>31.89357948303223</v>
       </c>
       <c r="C195" t="n">
-        <v>19.91597747802734</v>
+        <v>33.58864593505859</v>
       </c>
       <c r="D195" t="n">
-        <v>33.86308670043945</v>
+        <v>31.59372520446777</v>
       </c>
       <c r="E195" t="n">
-        <v>1.463534355163574</v>
+        <v>-4.321839332580566</v>
       </c>
       <c r="F195" t="n">
-        <v>7.348423004150391</v>
+        <v>-3.637434005737305</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>34.2100715637207</v>
+        <v>36.90080261230469</v>
       </c>
       <c r="B196" t="n">
-        <v>39.15714645385742</v>
+        <v>32.21165466308594</v>
       </c>
       <c r="C196" t="n">
-        <v>12.47822856903076</v>
+        <v>25.6479606628418</v>
       </c>
       <c r="D196" t="n">
-        <v>26.61813735961914</v>
+        <v>24.25585556030273</v>
       </c>
       <c r="E196" t="n">
-        <v>0.5268259048461914</v>
+        <v>-7.351360321044922</v>
       </c>
       <c r="F196" t="n">
-        <v>5.648149490356445</v>
+        <v>-6.542977809906006</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>35.24451065063477</v>
+        <v>36.74773025512695</v>
       </c>
       <c r="B197" t="n">
-        <v>39.66875839233398</v>
+        <v>32.45669174194336</v>
       </c>
       <c r="C197" t="n">
-        <v>5.55516529083252</v>
+        <v>17.55132102966309</v>
       </c>
       <c r="D197" t="n">
-        <v>18.83430480957031</v>
+        <v>16.57960891723633</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.7634339332580566</v>
+        <v>-9.570436477661133</v>
       </c>
       <c r="F197" t="n">
-        <v>3.863333702087402</v>
+        <v>-8.600838661193848</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>35.22126388549805</v>
+        <v>36.31248474121094</v>
       </c>
       <c r="B198" t="n">
-        <v>39.6561393737793</v>
+        <v>32.37009429931641</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.02134436182677746</v>
+        <v>11.56810188293457</v>
       </c>
       <c r="D198" t="n">
-        <v>11.45392799377441</v>
+        <v>9.753308296203613</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.884009838104248</v>
+        <v>-10.76817989349365</v>
       </c>
       <c r="F198" t="n">
-        <v>2.356451988220215</v>
+        <v>-10.25814819335938</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>35.93233489990234</v>
+        <v>36.60918045043945</v>
       </c>
       <c r="B199" t="n">
-        <v>39.65305709838867</v>
+        <v>32.31488418579102</v>
       </c>
       <c r="C199" t="n">
-        <v>-4.308178901672363</v>
+        <v>7.464770317077637</v>
       </c>
       <c r="D199" t="n">
-        <v>4.752453804016113</v>
+        <v>4.56949520111084</v>
       </c>
       <c r="E199" t="n">
-        <v>-1.239588737487793</v>
+        <v>-12.6550178527832</v>
       </c>
       <c r="F199" t="n">
-        <v>1.06243360042572</v>
+        <v>-12.80607414245605</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>36.3364143371582</v>
+        <v>36.48038482666016</v>
       </c>
       <c r="B200" t="n">
-        <v>39.44305801391602</v>
+        <v>32.92619323730469</v>
       </c>
       <c r="C200" t="n">
-        <v>-6.625699043273926</v>
+        <v>5.33072566986084</v>
       </c>
       <c r="D200" t="n">
-        <v>1.222676396369934</v>
+        <v>1.044510960578918</v>
       </c>
       <c r="E200" t="n">
-        <v>-1.634783744812012</v>
+        <v>-13.21547222137451</v>
       </c>
       <c r="F200" t="n">
-        <v>0.870973527431488</v>
+        <v>-13.98474788665771</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>37.11360168457031</v>
+        <v>36.88497543334961</v>
       </c>
       <c r="B201" t="n">
-        <v>39.29376220703125</v>
+        <v>33.06373596191406</v>
       </c>
       <c r="C201" t="n">
-        <v>-7.627734184265137</v>
+        <v>4.46751880645752</v>
       </c>
       <c r="D201" t="n">
-        <v>-1.199168086051941</v>
+        <v>0.1833926439285278</v>
       </c>
       <c r="E201" t="n">
-        <v>-1.652053356170654</v>
+        <v>-13.8665599822998</v>
       </c>
       <c r="F201" t="n">
-        <v>0.6952757239341736</v>
+        <v>-15.41290092468262</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>37.31078720092773</v>
+        <v>38.78824234008789</v>
       </c>
       <c r="B202" t="n">
-        <v>39.12477111816406</v>
+        <v>33.83060455322266</v>
       </c>
       <c r="C202" t="n">
-        <v>-6.673331260681152</v>
+        <v>4.59400463104248</v>
       </c>
       <c r="D202" t="n">
-        <v>-1.314823985099792</v>
+        <v>-0.182515025138855</v>
       </c>
       <c r="E202" t="n">
-        <v>-3.41400671005249</v>
+        <v>-14.57997894287109</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.5922117829322815</v>
+        <v>-16.15087127685547</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>38.00520706176758</v>
+        <v>40.66909790039062</v>
       </c>
       <c r="B203" t="n">
-        <v>39.13852310180664</v>
+        <v>35.52460479736328</v>
       </c>
       <c r="C203" t="n">
-        <v>-4.401928901672363</v>
+        <v>6.648144721984863</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.3711251020431519</v>
+        <v>1.119580388069153</v>
       </c>
       <c r="E203" t="n">
-        <v>-5.406579494476318</v>
+        <v>-15.46705055236816</v>
       </c>
       <c r="F203" t="n">
-        <v>-1.97485888004303</v>
+        <v>-16.51254653930664</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>38.03490829467773</v>
+        <v>41.65888214111328</v>
       </c>
       <c r="B204" t="n">
-        <v>40.44367218017578</v>
+        <v>37.20527267456055</v>
       </c>
       <c r="C204" t="n">
-        <v>-1.938464283943176</v>
+        <v>9.032448768615723</v>
       </c>
       <c r="D204" t="n">
-        <v>1.960795521736145</v>
+        <v>4.766720771789551</v>
       </c>
       <c r="E204" t="n">
-        <v>-7.444470882415771</v>
+        <v>-16.15630912780762</v>
       </c>
       <c r="F204" t="n">
-        <v>-4.065510749816895</v>
+        <v>-18.48351097106934</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>38.41819381713867</v>
+        <v>42.97901916503906</v>
       </c>
       <c r="B205" t="n">
-        <v>40.68537521362305</v>
+        <v>39.06541442871094</v>
       </c>
       <c r="C205" t="n">
-        <v>0.8231170773506165</v>
+        <v>11.81301307678223</v>
       </c>
       <c r="D205" t="n">
-        <v>3.921576738357544</v>
+        <v>7.839827537536621</v>
       </c>
       <c r="E205" t="n">
-        <v>-9.561720848083496</v>
+        <v>-18.26938819885254</v>
       </c>
       <c r="F205" t="n">
-        <v>-7.147964477539062</v>
+        <v>-19.33733367919922</v>
       </c>
     </row>
   </sheetData>
